--- a/upload/voos_2026.xlsx
+++ b/upload/voos_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A42E3A9-7EB9-4913-8333-19CEED4A6BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7DF358A-EEBD-4274-B139-95A8791990A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1406" uniqueCount="143">
   <si>
     <t>Traslado do Exmo. Governador de Minas e Comitiva até as cidades de São Antônio do Monte e Serra da Saudade/MG</t>
   </si>
@@ -251,9 +251,6 @@
     <t>Secretaria de Estado de Desenvolvimento Econômico</t>
   </si>
   <si>
-    <t>Chefe</t>
-  </si>
-  <si>
     <t>Presidente</t>
   </si>
   <si>
@@ -261,6 +258,213 @@
   </si>
   <si>
     <t>Secretaria-Geral do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo. Sr. Governador do Estado de Minas Gerais e comitiva para as cidade de Brasília/DF.</t>
+  </si>
+  <si>
+    <t>BRASILIA</t>
+  </si>
+  <si>
+    <t>Pedro Bruno Barros de Souza</t>
+  </si>
+  <si>
+    <t>0011-2026</t>
+  </si>
+  <si>
+    <t>SAO JOAO DEL REI</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo sr. Governador do Estado de Minas Gerais e comitiva para a cidade de São João del-Rei/MG.</t>
+  </si>
+  <si>
+    <t>CARLOS FREDERICO OTONI GARCIA</t>
+  </si>
+  <si>
+    <t>Rubens Gonçalves de Brito</t>
+  </si>
+  <si>
+    <t>Rossieli Soares da Silva</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo. Governador de Minas e Comitiva até as cidades de Divinópolis, Oliveira, Governador Valadares, Ipatinga e Montes Claros/MG.</t>
+  </si>
+  <si>
+    <t>0018-2026</t>
+  </si>
+  <si>
+    <t>DIVINOPOLIS</t>
+  </si>
+  <si>
+    <t>Ana Carolina Pinto Caram Guimarães</t>
+  </si>
+  <si>
+    <t>0019-2026</t>
+  </si>
+  <si>
+    <t>OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Adelino Bento Júnior</t>
+  </si>
+  <si>
+    <t>3º Sgt PM</t>
+  </si>
+  <si>
+    <t>Glauber Pereira Vitor</t>
+  </si>
+  <si>
+    <t>Cerimonial</t>
+  </si>
+  <si>
+    <t>0020-2026</t>
+  </si>
+  <si>
+    <t>GOVERNADOR VALADARES</t>
+  </si>
+  <si>
+    <t>0022-2026</t>
+  </si>
+  <si>
+    <t>IPATINGA</t>
+  </si>
+  <si>
+    <t>MONTES CLAROS</t>
+  </si>
+  <si>
+    <t>0023-2026</t>
+  </si>
+  <si>
+    <t>Igor Augusto Tinoco da Silva</t>
+  </si>
+  <si>
+    <t>Imprensa</t>
+  </si>
+  <si>
+    <t>Aline Brandão Silva</t>
+  </si>
+  <si>
+    <t>Subsecretária de Cerimonial e Eventos</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo. Governador de Minas e comitiva para as cidades de Paracatu/MG, Unaí/MG e Brasília/DF</t>
+  </si>
+  <si>
+    <t>0029-2026</t>
+  </si>
+  <si>
+    <t>PARACATU</t>
+  </si>
+  <si>
+    <t>Letícia Baptista Gamboge Reis</t>
+  </si>
+  <si>
+    <t>0031-2026</t>
+  </si>
+  <si>
+    <t>JUIZ DE FORA</t>
+  </si>
+  <si>
+    <t>0033-2026</t>
+  </si>
+  <si>
+    <t>GOIANA</t>
+  </si>
+  <si>
+    <t>Jordana de Oliveira Filgueiras Daldegan</t>
+  </si>
+  <si>
+    <t>Corpo de Bombeiros do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Lucas Pinto Simões</t>
+  </si>
+  <si>
+    <t>Diana Wanderley Janhan Sousa</t>
+  </si>
+  <si>
+    <t>Cap BM</t>
+  </si>
+  <si>
+    <t>PP-IEG - GUARÁ 02</t>
+  </si>
+  <si>
+    <t>0045-2026</t>
+  </si>
+  <si>
+    <t>4ª BRAvE</t>
+  </si>
+  <si>
+    <t>Tentativa de ida até a cidade de Ubá com o Exmo Sr Governador, porém, devido às condições meteorológicas não foi possível prosseguir, tendo a equipe retornado ao aeroporto de Juiz de Fora após sobrevoo em áreas afetadas pelas chuvas dos últimos dias em Juiz de Fora.</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo Governador de Minas Gerais de Juiz de Fora até a cidade de Ubá. E1: 374,6 E2: 184,0 F1: 172,3 F2: 533,7</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo Governador de Minas Gerais de Juiz de Fora até a cidade de Ubá. E1: 375,5 E2: 184,8 F1: 172,6 F2: 534,1</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo Governador de Minas Gerais de Juiz de Fora até a cidade de Ubá. Traslado de SBZM para SJIM E1: 378,8 E2: 188,2 F1: 174,0 F2: 535,4</t>
+  </si>
+  <si>
+    <t>Joselito Oliveira de Paula</t>
+  </si>
+  <si>
+    <t>Cel BM</t>
+  </si>
+  <si>
+    <t>Victor Navarro dos Reis</t>
+  </si>
+  <si>
+    <t>1º Ten PM</t>
+  </si>
+  <si>
+    <t>Traslado do Exmo. Governador de Minas Gerais e comitiva para Araxá.</t>
+  </si>
+  <si>
+    <t>0034-2026</t>
+  </si>
+  <si>
+    <t>Andre Valadares da Cruz</t>
+  </si>
+  <si>
+    <t>0035-2026</t>
+  </si>
+  <si>
+    <t>Cap PM</t>
+  </si>
+  <si>
+    <t>0036-2026</t>
+  </si>
+  <si>
+    <t>0037-2026</t>
+  </si>
+  <si>
+    <t>UBA</t>
+  </si>
+  <si>
+    <t>Videomaker</t>
+  </si>
+  <si>
+    <t>Delegada-Geral</t>
+  </si>
+  <si>
+    <t>Polícia Civil do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Polícia Militar do Estado de Minas Gerais</t>
+  </si>
+  <si>
+    <t>Secretaria de Estado de Educação</t>
+  </si>
+  <si>
+    <t>Secretaria de Estado de Infraestrutura e Mobilidade</t>
+  </si>
+  <si>
+    <t>Chefe do Gabinete Militar do Governador</t>
+  </si>
+  <si>
+    <t>Comandante-Geral</t>
   </si>
 </sst>
 </file>
@@ -268,7 +472,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -747,17 +951,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Ênfase1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1079,14 +1276,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46D67731-6C8F-4D19-B5E9-3D6FBC4AC40F}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="13.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="26.85546875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="42.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.140625" customWidth="1"/>
+    <col min="10" max="10" width="56.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="64.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1151,13 +1352,13 @@
         <v>61</v>
       </c>
       <c r="I2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -1186,13 +1387,13 @@
         <v>61</v>
       </c>
       <c r="I3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="K3" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1221,13 +1422,13 @@
         <v>61</v>
       </c>
       <c r="I4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J4" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="K4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1256,13 +1457,13 @@
         <v>61</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K5" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -1291,13 +1492,13 @@
         <v>61</v>
       </c>
       <c r="I6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="K6" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1332,7 +1533,7 @@
         <v>6</v>
       </c>
       <c r="K7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1361,13 +1562,13 @@
         <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1431,13 +1632,13 @@
         <v>19</v>
       </c>
       <c r="I10" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="K10" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1466,10 +1667,10 @@
         <v>19</v>
       </c>
       <c r="I11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K11" t="s">
         <v>45</v>
@@ -1501,13 +1702,13 @@
         <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J12" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="K12" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1536,13 +1737,13 @@
         <v>19</v>
       </c>
       <c r="I13" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K13" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1577,7 +1778,7 @@
         <v>6</v>
       </c>
       <c r="K14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1606,13 +1807,13 @@
         <v>5</v>
       </c>
       <c r="I15" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J15" t="s">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="K15" t="s">
-        <v>67</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1641,13 +1842,13 @@
         <v>5</v>
       </c>
       <c r="I16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J16" t="s">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="K16" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1679,7 +1880,7 @@
         <v>16</v>
       </c>
       <c r="J17" t="s">
-        <v>71</v>
+        <v>141</v>
       </c>
       <c r="K17" t="s">
         <v>63</v>
@@ -1746,13 +1947,13 @@
         <v>5</v>
       </c>
       <c r="I19" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="5" t="s">
-        <v>65</v>
+        <v>8</v>
+      </c>
+      <c r="J19" t="s">
+        <v>71</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1783,11 +1984,11 @@
       <c r="I20" t="s">
         <v>1</v>
       </c>
-      <c r="J20" s="6" t="s">
+      <c r="J20" t="s">
         <v>6</v>
       </c>
       <c r="K20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1818,7 +2019,7 @@
       <c r="I21" t="s">
         <v>32</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" t="s">
         <v>64</v>
       </c>
       <c r="K21" t="s">
@@ -1851,13 +2052,13 @@
         <v>19</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="K22" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1888,7 +2089,7 @@
       <c r="I23" t="s">
         <v>22</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="J23" t="s">
         <v>62</v>
       </c>
       <c r="K23" t="s">
@@ -1921,13 +2122,13 @@
         <v>19</v>
       </c>
       <c r="I24" t="s">
-        <v>26</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>27</v>
+        <v>34</v>
+      </c>
+      <c r="J24" t="s">
+        <v>62</v>
       </c>
       <c r="K24" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1991,13 +2192,13 @@
         <v>19</v>
       </c>
       <c r="I26" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J26" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="K26" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -2032,7 +2233,7 @@
         <v>6</v>
       </c>
       <c r="K27" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2096,13 +2297,13 @@
         <v>36</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K29" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2131,13 +2332,13 @@
         <v>36</v>
       </c>
       <c r="I30" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="J30" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="K30" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2166,13 +2367,13 @@
         <v>36</v>
       </c>
       <c r="I31" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J31" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="K31" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2207,7 +2408,7 @@
         <v>6</v>
       </c>
       <c r="K32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2271,13 +2472,13 @@
         <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K34" t="s">
-        <v>40</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2341,13 +2542,13 @@
         <v>39</v>
       </c>
       <c r="I36" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="J36" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="K36" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2376,13 +2577,13 @@
         <v>39</v>
       </c>
       <c r="I37" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="J37" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2411,13 +2612,13 @@
         <v>39</v>
       </c>
       <c r="I38" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J38" t="s">
-        <v>65</v>
-      </c>
-      <c r="K38" s="8" t="s">
-        <v>74</v>
+        <v>27</v>
+      </c>
+      <c r="K38" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2451,8 +2652,8 @@
       <c r="J39" t="s">
         <v>6</v>
       </c>
-      <c r="K39" s="8" t="s">
-        <v>74</v>
+      <c r="K39" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2486,7 +2687,7 @@
       <c r="J40" t="s">
         <v>64</v>
       </c>
-      <c r="K40" s="8" t="s">
+      <c r="K40" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2516,47 +2717,47 @@
         <v>47</v>
       </c>
       <c r="I41" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>44</v>
-      </c>
-      <c r="K41" s="8" t="s">
-        <v>45</v>
+        <v>65</v>
+      </c>
+      <c r="K41" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B42" s="1">
-        <v>2.9166666666666664E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F42" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G42" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H42" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="I42" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J42" t="s">
-        <v>27</v>
-      </c>
-      <c r="K42" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K42" t="s">
         <v>45</v>
       </c>
     </row>
@@ -2586,13 +2787,13 @@
         <v>47</v>
       </c>
       <c r="I43" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J43" t="s">
-        <v>65</v>
-      </c>
-      <c r="K43" s="8" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="K43" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2621,83 +2822,83 @@
         <v>47</v>
       </c>
       <c r="I44" t="s">
-        <v>21</v>
-      </c>
-      <c r="J44" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J44" t="s">
         <v>65</v>
       </c>
-      <c r="K44" s="9" t="s">
-        <v>74</v>
+      <c r="K44" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B45" s="1">
-        <v>2.9166666666666664E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
         <v>46</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F45" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G45" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="H45" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s">
-        <v>1</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="K45" s="9" t="s">
-        <v>74</v>
+        <v>13</v>
+      </c>
+      <c r="J45" t="s">
+        <v>65</v>
+      </c>
+      <c r="K45" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B46" s="1">
-        <v>2.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F46" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G46" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H46" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I46" t="s">
-        <v>32</v>
-      </c>
-      <c r="J46" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="K46" s="9" t="s">
-        <v>63</v>
+        <v>26</v>
+      </c>
+      <c r="J46" t="s">
+        <v>27</v>
+      </c>
+      <c r="K46" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2705,13 +2906,13 @@
         <v>28</v>
       </c>
       <c r="B47" s="1">
-        <v>2.4999999999999998E-2</v>
+        <v>2.9166666666666664E-2</v>
       </c>
       <c r="C47" t="s">
         <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E47" t="s">
         <v>31</v>
@@ -2720,164 +2921,3839 @@
         <v>46051</v>
       </c>
       <c r="G47" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" t="s">
         <v>47</v>
       </c>
-      <c r="H47" t="s">
-        <v>49</v>
-      </c>
       <c r="I47" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="K47" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="J47" t="s">
+        <v>27</v>
+      </c>
+      <c r="K47" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B48" s="1">
-        <v>2.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C48" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D48" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F48" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G48" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H48" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I48" t="s">
-        <v>26</v>
-      </c>
-      <c r="J48" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K48" s="9" t="s">
-        <v>45</v>
+        <v>76</v>
+      </c>
+      <c r="J48" t="s">
+        <v>62</v>
+      </c>
+      <c r="K48" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B49" s="1">
-        <v>2.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F49" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G49" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I49" t="s">
-        <v>41</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K49" s="9" t="s">
-        <v>42</v>
+        <v>23</v>
+      </c>
+      <c r="J49" t="s">
+        <v>24</v>
+      </c>
+      <c r="K49" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B50" s="1">
-        <v>2.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D50" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F50" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G50" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H50" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I50" t="s">
-        <v>21</v>
-      </c>
-      <c r="J50" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="K50" s="9" t="s">
-        <v>74</v>
+        <v>7</v>
+      </c>
+      <c r="J50" t="s">
+        <v>64</v>
+      </c>
+      <c r="K50" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="B51" s="1">
-        <v>2.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="F51" s="2">
-        <v>46051</v>
+        <v>46056</v>
       </c>
       <c r="G51" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="H51" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="I51" t="s">
         <v>1</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="J51" t="s">
         <v>6</v>
       </c>
-      <c r="K51" s="9" t="s">
+      <c r="K51" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="B52" s="1">
+        <v>2.9166666666666664E-2</v>
+      </c>
+      <c r="C52" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G52" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52" t="s">
+        <v>47</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
+        <v>6</v>
+      </c>
+      <c r="K52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="B53" s="1">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" t="s">
+        <v>48</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G53" t="s">
+        <v>47</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
+      </c>
+      <c r="I53" t="s">
+        <v>32</v>
+      </c>
+      <c r="J53" t="s">
+        <v>64</v>
+      </c>
+      <c r="K53" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>28</v>
+      </c>
+      <c r="B54" s="1">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" t="s">
+        <v>48</v>
+      </c>
+      <c r="E54" t="s">
+        <v>31</v>
+      </c>
+      <c r="F54" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G54" t="s">
+        <v>47</v>
+      </c>
+      <c r="H54" t="s">
+        <v>49</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>65</v>
+      </c>
+      <c r="K54" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="1">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="C55" t="s">
+        <v>29</v>
+      </c>
+      <c r="D55" t="s">
+        <v>48</v>
+      </c>
+      <c r="E55" t="s">
+        <v>31</v>
+      </c>
+      <c r="F55" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G55" t="s">
+        <v>47</v>
+      </c>
+      <c r="H55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I55" t="s">
+        <v>43</v>
+      </c>
+      <c r="J55" t="s">
+        <v>44</v>
+      </c>
+      <c r="K55" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>28</v>
+      </c>
+      <c r="B56" s="1">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="C56" t="s">
+        <v>29</v>
+      </c>
+      <c r="D56" t="s">
+        <v>48</v>
+      </c>
+      <c r="E56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G56" t="s">
+        <v>47</v>
+      </c>
+      <c r="H56" t="s">
+        <v>49</v>
+      </c>
+      <c r="I56" t="s">
+        <v>41</v>
+      </c>
+      <c r="J56" t="s">
+        <v>65</v>
+      </c>
+      <c r="K56" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
         <v>74</v>
+      </c>
+      <c r="B57" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C57" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" t="s">
+        <v>48</v>
+      </c>
+      <c r="E57" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G57" t="s">
+        <v>75</v>
+      </c>
+      <c r="H57" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" t="s">
+        <v>65</v>
+      </c>
+      <c r="K57" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>28</v>
+      </c>
+      <c r="B58" s="1">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="C58" t="s">
+        <v>29</v>
+      </c>
+      <c r="D58" t="s">
+        <v>48</v>
+      </c>
+      <c r="E58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G58" t="s">
+        <v>47</v>
+      </c>
+      <c r="H58" t="s">
+        <v>49</v>
+      </c>
+      <c r="I58" t="s">
+        <v>26</v>
+      </c>
+      <c r="J58" t="s">
+        <v>27</v>
+      </c>
+      <c r="K58" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>74</v>
+      </c>
+      <c r="B59" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C59" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" t="s">
+        <v>48</v>
+      </c>
+      <c r="E59" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G59" t="s">
+        <v>75</v>
+      </c>
+      <c r="H59" t="s">
+        <v>5</v>
+      </c>
+      <c r="I59" t="s">
+        <v>26</v>
+      </c>
+      <c r="J59" t="s">
+        <v>27</v>
+      </c>
+      <c r="K59" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>74</v>
+      </c>
+      <c r="B60" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C60" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" t="s">
+        <v>48</v>
+      </c>
+      <c r="E60" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G60" t="s">
+        <v>75</v>
+      </c>
+      <c r="H60" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" t="s">
+        <v>76</v>
+      </c>
+      <c r="J60" t="s">
+        <v>62</v>
+      </c>
+      <c r="K60" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C61" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" t="s">
+        <v>48</v>
+      </c>
+      <c r="E61" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G61" t="s">
+        <v>75</v>
+      </c>
+      <c r="H61" t="s">
+        <v>5</v>
+      </c>
+      <c r="I61" t="s">
+        <v>23</v>
+      </c>
+      <c r="J61" t="s">
+        <v>24</v>
+      </c>
+      <c r="K61" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>74</v>
+      </c>
+      <c r="B62" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C62" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" t="s">
+        <v>48</v>
+      </c>
+      <c r="E62" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G62" t="s">
+        <v>75</v>
+      </c>
+      <c r="H62" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" t="s">
+        <v>7</v>
+      </c>
+      <c r="J62" t="s">
+        <v>64</v>
+      </c>
+      <c r="K62" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>28</v>
+      </c>
+      <c r="B63" s="1">
+        <v>2.4999999999999998E-2</v>
+      </c>
+      <c r="C63" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" t="s">
+        <v>48</v>
+      </c>
+      <c r="E63" t="s">
+        <v>31</v>
+      </c>
+      <c r="F63" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G63" t="s">
+        <v>47</v>
+      </c>
+      <c r="H63" t="s">
+        <v>49</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>6</v>
+      </c>
+      <c r="K63" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="1">
+        <v>6.25E-2</v>
+      </c>
+      <c r="C64" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" t="s">
+        <v>48</v>
+      </c>
+      <c r="E64" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64" s="2">
+        <v>46056</v>
+      </c>
+      <c r="G64" t="s">
+        <v>75</v>
+      </c>
+      <c r="H64" t="s">
+        <v>5</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
+        <v>6</v>
+      </c>
+      <c r="K64" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>79</v>
+      </c>
+      <c r="B65" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C65" t="s">
+        <v>17</v>
+      </c>
+      <c r="D65" t="s">
+        <v>77</v>
+      </c>
+      <c r="E65" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G65" t="s">
+        <v>5</v>
+      </c>
+      <c r="H65" t="s">
+        <v>78</v>
+      </c>
+      <c r="I65" t="s">
+        <v>80</v>
+      </c>
+      <c r="J65" t="s">
+        <v>142</v>
+      </c>
+      <c r="K65" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C66" t="s">
+        <v>17</v>
+      </c>
+      <c r="D66" t="s">
+        <v>77</v>
+      </c>
+      <c r="E66" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G66" t="s">
+        <v>5</v>
+      </c>
+      <c r="H66" t="s">
+        <v>78</v>
+      </c>
+      <c r="I66" t="s">
+        <v>13</v>
+      </c>
+      <c r="J66" t="s">
+        <v>65</v>
+      </c>
+      <c r="K66" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>79</v>
+      </c>
+      <c r="B67" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C67" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G67" t="s">
+        <v>5</v>
+      </c>
+      <c r="H67" t="s">
+        <v>78</v>
+      </c>
+      <c r="I67" t="s">
+        <v>16</v>
+      </c>
+      <c r="J67" t="s">
+        <v>141</v>
+      </c>
+      <c r="K67" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>79</v>
+      </c>
+      <c r="B68" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C68" t="s">
+        <v>17</v>
+      </c>
+      <c r="D68" t="s">
+        <v>77</v>
+      </c>
+      <c r="E68" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G68" t="s">
+        <v>5</v>
+      </c>
+      <c r="H68" t="s">
+        <v>78</v>
+      </c>
+      <c r="I68" t="s">
+        <v>7</v>
+      </c>
+      <c r="J68" t="s">
+        <v>64</v>
+      </c>
+      <c r="K68" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>79</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C69" t="s">
+        <v>17</v>
+      </c>
+      <c r="D69" t="s">
+        <v>77</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G69" t="s">
+        <v>5</v>
+      </c>
+      <c r="H69" t="s">
+        <v>78</v>
+      </c>
+      <c r="I69" t="s">
+        <v>1</v>
+      </c>
+      <c r="J69" t="s">
+        <v>6</v>
+      </c>
+      <c r="K69" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>79</v>
+      </c>
+      <c r="B70" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C70" t="s">
+        <v>17</v>
+      </c>
+      <c r="D70" t="s">
+        <v>77</v>
+      </c>
+      <c r="E70" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G70" t="s">
+        <v>5</v>
+      </c>
+      <c r="H70" t="s">
+        <v>78</v>
+      </c>
+      <c r="I70" t="s">
+        <v>82</v>
+      </c>
+      <c r="J70" t="s">
+        <v>62</v>
+      </c>
+      <c r="K70" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="C71" t="s">
+        <v>17</v>
+      </c>
+      <c r="D71" t="s">
+        <v>77</v>
+      </c>
+      <c r="E71" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G71" t="s">
+        <v>5</v>
+      </c>
+      <c r="H71" t="s">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s">
+        <v>81</v>
+      </c>
+      <c r="J71" t="s">
+        <v>12</v>
+      </c>
+      <c r="K71" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>83</v>
+      </c>
+      <c r="B72" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C72" t="s">
+        <v>29</v>
+      </c>
+      <c r="D72" t="s">
+        <v>84</v>
+      </c>
+      <c r="E72" t="s">
+        <v>31</v>
+      </c>
+      <c r="F72" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G72" t="s">
+        <v>5</v>
+      </c>
+      <c r="H72" t="s">
+        <v>85</v>
+      </c>
+      <c r="I72" t="s">
+        <v>32</v>
+      </c>
+      <c r="J72" t="s">
+        <v>64</v>
+      </c>
+      <c r="K72" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>120</v>
+      </c>
+      <c r="B73" s="1">
+        <v>2.5694444444444443E-2</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" t="s">
+        <v>84</v>
+      </c>
+      <c r="E73" t="s">
+        <v>4</v>
+      </c>
+      <c r="F73" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G73" t="s">
+        <v>108</v>
+      </c>
+      <c r="H73" t="s">
+        <v>134</v>
+      </c>
+      <c r="I73" t="s">
+        <v>32</v>
+      </c>
+      <c r="J73" t="s">
+        <v>64</v>
+      </c>
+      <c r="K73" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>83</v>
+      </c>
+      <c r="B74" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C74" t="s">
+        <v>29</v>
+      </c>
+      <c r="D74" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" t="s">
+        <v>31</v>
+      </c>
+      <c r="F74" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G74" t="s">
+        <v>5</v>
+      </c>
+      <c r="H74" t="s">
+        <v>85</v>
+      </c>
+      <c r="I74" t="s">
+        <v>86</v>
+      </c>
+      <c r="J74" t="s">
+        <v>12</v>
+      </c>
+      <c r="K74" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C75" t="s">
+        <v>29</v>
+      </c>
+      <c r="D75" t="s">
+        <v>84</v>
+      </c>
+      <c r="E75" t="s">
+        <v>31</v>
+      </c>
+      <c r="F75" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G75" t="s">
+        <v>5</v>
+      </c>
+      <c r="H75" t="s">
+        <v>85</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>65</v>
+      </c>
+      <c r="K75" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>120</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2.5694444444444443E-2</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" t="s">
+        <v>84</v>
+      </c>
+      <c r="E76" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G76" t="s">
+        <v>108</v>
+      </c>
+      <c r="H76" t="s">
+        <v>134</v>
+      </c>
+      <c r="I76" t="s">
+        <v>13</v>
+      </c>
+      <c r="J76" t="s">
+        <v>65</v>
+      </c>
+      <c r="K76" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C77" t="s">
+        <v>29</v>
+      </c>
+      <c r="D77" t="s">
+        <v>84</v>
+      </c>
+      <c r="E77" t="s">
+        <v>31</v>
+      </c>
+      <c r="F77" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G77" t="s">
+        <v>5</v>
+      </c>
+      <c r="H77" t="s">
+        <v>85</v>
+      </c>
+      <c r="I77" t="s">
+        <v>25</v>
+      </c>
+      <c r="J77" t="s">
+        <v>62</v>
+      </c>
+      <c r="K77" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>120</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2.5694444444444443E-2</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" t="s">
+        <v>84</v>
+      </c>
+      <c r="E78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G78" t="s">
+        <v>108</v>
+      </c>
+      <c r="H78" t="s">
+        <v>134</v>
+      </c>
+      <c r="I78" t="s">
+        <v>111</v>
+      </c>
+      <c r="J78" t="s">
+        <v>142</v>
+      </c>
+      <c r="K78" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>120</v>
+      </c>
+      <c r="B79" s="1">
+        <v>2.5694444444444443E-2</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>84</v>
+      </c>
+      <c r="E79" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G79" t="s">
+        <v>108</v>
+      </c>
+      <c r="H79" t="s">
+        <v>134</v>
+      </c>
+      <c r="I79" t="s">
+        <v>113</v>
+      </c>
+      <c r="J79" t="s">
+        <v>100</v>
+      </c>
+      <c r="K79" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>83</v>
+      </c>
+      <c r="B80" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C80" t="s">
+        <v>29</v>
+      </c>
+      <c r="D80" t="s">
+        <v>84</v>
+      </c>
+      <c r="E80" t="s">
+        <v>31</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G80" t="s">
+        <v>5</v>
+      </c>
+      <c r="H80" t="s">
+        <v>85</v>
+      </c>
+      <c r="I80" t="s">
+        <v>16</v>
+      </c>
+      <c r="J80" t="s">
+        <v>141</v>
+      </c>
+      <c r="K80" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>120</v>
+      </c>
+      <c r="B81" s="1">
+        <v>2.5694444444444443E-2</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" t="s">
+        <v>84</v>
+      </c>
+      <c r="E81" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G81" t="s">
+        <v>108</v>
+      </c>
+      <c r="H81" t="s">
+        <v>134</v>
+      </c>
+      <c r="I81" t="s">
+        <v>16</v>
+      </c>
+      <c r="J81" t="s">
+        <v>141</v>
+      </c>
+      <c r="K81" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>83</v>
+      </c>
+      <c r="B82" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C82" t="s">
+        <v>29</v>
+      </c>
+      <c r="D82" t="s">
+        <v>84</v>
+      </c>
+      <c r="E82" t="s">
+        <v>31</v>
+      </c>
+      <c r="F82" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G82" t="s">
+        <v>5</v>
+      </c>
+      <c r="H82" t="s">
+        <v>85</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1</v>
+      </c>
+      <c r="J82" t="s">
+        <v>6</v>
+      </c>
+      <c r="K82" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>120</v>
+      </c>
+      <c r="B83" s="1">
+        <v>2.5694444444444443E-2</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" t="s">
+        <v>84</v>
+      </c>
+      <c r="E83" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G83" t="s">
+        <v>108</v>
+      </c>
+      <c r="H83" t="s">
+        <v>134</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1</v>
+      </c>
+      <c r="J83" t="s">
+        <v>6</v>
+      </c>
+      <c r="K83" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C84" t="s">
+        <v>29</v>
+      </c>
+      <c r="D84" t="s">
+        <v>84</v>
+      </c>
+      <c r="E84" t="s">
+        <v>31</v>
+      </c>
+      <c r="F84" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G84" t="s">
+        <v>5</v>
+      </c>
+      <c r="H84" t="s">
+        <v>85</v>
+      </c>
+      <c r="I84" t="s">
+        <v>81</v>
+      </c>
+      <c r="J84" t="s">
+        <v>12</v>
+      </c>
+      <c r="K84" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>83</v>
+      </c>
+      <c r="B85" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C85" t="s">
+        <v>29</v>
+      </c>
+      <c r="D85" t="s">
+        <v>87</v>
+      </c>
+      <c r="E85" t="s">
+        <v>31</v>
+      </c>
+      <c r="F85" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G85" t="s">
+        <v>85</v>
+      </c>
+      <c r="H85" t="s">
+        <v>88</v>
+      </c>
+      <c r="I85" t="s">
+        <v>89</v>
+      </c>
+      <c r="J85" t="s">
+        <v>90</v>
+      </c>
+      <c r="K85" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>121</v>
+      </c>
+      <c r="B86" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>87</v>
+      </c>
+      <c r="E86" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G86" t="s">
+        <v>134</v>
+      </c>
+      <c r="H86" t="s">
+        <v>110</v>
+      </c>
+      <c r="I86" t="s">
+        <v>32</v>
+      </c>
+      <c r="J86" t="s">
+        <v>64</v>
+      </c>
+      <c r="K86" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>83</v>
+      </c>
+      <c r="B87" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C87" t="s">
+        <v>29</v>
+      </c>
+      <c r="D87" t="s">
+        <v>87</v>
+      </c>
+      <c r="E87" t="s">
+        <v>31</v>
+      </c>
+      <c r="F87" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G87" t="s">
+        <v>85</v>
+      </c>
+      <c r="H87" t="s">
+        <v>88</v>
+      </c>
+      <c r="I87" t="s">
+        <v>32</v>
+      </c>
+      <c r="J87" t="s">
+        <v>64</v>
+      </c>
+      <c r="K87" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>83</v>
+      </c>
+      <c r="B88" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C88" t="s">
+        <v>29</v>
+      </c>
+      <c r="D88" t="s">
+        <v>87</v>
+      </c>
+      <c r="E88" t="s">
+        <v>31</v>
+      </c>
+      <c r="F88" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G88" t="s">
+        <v>85</v>
+      </c>
+      <c r="H88" t="s">
+        <v>88</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>65</v>
+      </c>
+      <c r="K88" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>87</v>
+      </c>
+      <c r="E89" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G89" t="s">
+        <v>134</v>
+      </c>
+      <c r="H89" t="s">
+        <v>110</v>
+      </c>
+      <c r="I89" t="s">
+        <v>13</v>
+      </c>
+      <c r="J89" t="s">
+        <v>65</v>
+      </c>
+      <c r="K89" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>83</v>
+      </c>
+      <c r="B90" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C90" t="s">
+        <v>29</v>
+      </c>
+      <c r="D90" t="s">
+        <v>87</v>
+      </c>
+      <c r="E90" t="s">
+        <v>31</v>
+      </c>
+      <c r="F90" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G90" t="s">
+        <v>85</v>
+      </c>
+      <c r="H90" t="s">
+        <v>88</v>
+      </c>
+      <c r="I90" t="s">
+        <v>91</v>
+      </c>
+      <c r="J90" t="s">
+        <v>92</v>
+      </c>
+      <c r="K90" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>121</v>
+      </c>
+      <c r="B91" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
+        <v>87</v>
+      </c>
+      <c r="E91" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G91" t="s">
+        <v>134</v>
+      </c>
+      <c r="H91" t="s">
+        <v>110</v>
+      </c>
+      <c r="I91" t="s">
+        <v>111</v>
+      </c>
+      <c r="J91" t="s">
+        <v>142</v>
+      </c>
+      <c r="K91" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>87</v>
+      </c>
+      <c r="E92" t="s">
+        <v>4</v>
+      </c>
+      <c r="F92" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G92" t="s">
+        <v>134</v>
+      </c>
+      <c r="H92" t="s">
+        <v>110</v>
+      </c>
+      <c r="I92" t="s">
+        <v>113</v>
+      </c>
+      <c r="J92" t="s">
+        <v>100</v>
+      </c>
+      <c r="K92" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>121</v>
+      </c>
+      <c r="B93" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
+        <v>87</v>
+      </c>
+      <c r="E93" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G93" t="s">
+        <v>134</v>
+      </c>
+      <c r="H93" t="s">
+        <v>110</v>
+      </c>
+      <c r="I93" t="s">
+        <v>16</v>
+      </c>
+      <c r="J93" t="s">
+        <v>141</v>
+      </c>
+      <c r="K93" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>121</v>
+      </c>
+      <c r="B94" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>87</v>
+      </c>
+      <c r="E94" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G94" t="s">
+        <v>134</v>
+      </c>
+      <c r="H94" t="s">
+        <v>110</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1</v>
+      </c>
+      <c r="J94" t="s">
+        <v>6</v>
+      </c>
+      <c r="K94" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>83</v>
+      </c>
+      <c r="B95" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C95" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95" t="s">
+        <v>87</v>
+      </c>
+      <c r="E95" t="s">
+        <v>31</v>
+      </c>
+      <c r="F95" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G95" t="s">
+        <v>85</v>
+      </c>
+      <c r="H95" t="s">
+        <v>88</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1</v>
+      </c>
+      <c r="J95" t="s">
+        <v>6</v>
+      </c>
+      <c r="K95" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>83</v>
+      </c>
+      <c r="B96" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C96" t="s">
+        <v>29</v>
+      </c>
+      <c r="D96" t="s">
+        <v>93</v>
+      </c>
+      <c r="E96" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G96" t="s">
+        <v>88</v>
+      </c>
+      <c r="H96" t="s">
+        <v>94</v>
+      </c>
+      <c r="I96" t="s">
+        <v>32</v>
+      </c>
+      <c r="J96" t="s">
+        <v>64</v>
+      </c>
+      <c r="K96" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>83</v>
+      </c>
+      <c r="B97" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C97" t="s">
+        <v>29</v>
+      </c>
+      <c r="D97" t="s">
+        <v>93</v>
+      </c>
+      <c r="E97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G97" t="s">
+        <v>88</v>
+      </c>
+      <c r="H97" t="s">
+        <v>94</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s">
+        <v>65</v>
+      </c>
+      <c r="K97" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>83</v>
+      </c>
+      <c r="B98" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C98" t="s">
+        <v>29</v>
+      </c>
+      <c r="D98" t="s">
+        <v>93</v>
+      </c>
+      <c r="E98" t="s">
+        <v>31</v>
+      </c>
+      <c r="F98" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G98" t="s">
+        <v>88</v>
+      </c>
+      <c r="H98" t="s">
+        <v>94</v>
+      </c>
+      <c r="I98" t="s">
+        <v>91</v>
+      </c>
+      <c r="J98" t="s">
+        <v>92</v>
+      </c>
+      <c r="K98" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>83</v>
+      </c>
+      <c r="B99" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C99" t="s">
+        <v>29</v>
+      </c>
+      <c r="D99" t="s">
+        <v>93</v>
+      </c>
+      <c r="E99" t="s">
+        <v>31</v>
+      </c>
+      <c r="F99" s="2">
+        <v>46063</v>
+      </c>
+      <c r="G99" t="s">
+        <v>88</v>
+      </c>
+      <c r="H99" t="s">
+        <v>94</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1</v>
+      </c>
+      <c r="J99" t="s">
+        <v>6</v>
+      </c>
+      <c r="K99" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>83</v>
+      </c>
+      <c r="B100" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C100" t="s">
+        <v>29</v>
+      </c>
+      <c r="D100" t="s">
+        <v>95</v>
+      </c>
+      <c r="E100" t="s">
+        <v>31</v>
+      </c>
+      <c r="F100" s="2">
+        <v>46064</v>
+      </c>
+      <c r="G100" t="s">
+        <v>96</v>
+      </c>
+      <c r="H100" t="s">
+        <v>97</v>
+      </c>
+      <c r="I100" t="s">
+        <v>32</v>
+      </c>
+      <c r="J100" t="s">
+        <v>64</v>
+      </c>
+      <c r="K100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>83</v>
+      </c>
+      <c r="B101" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C101" t="s">
+        <v>29</v>
+      </c>
+      <c r="D101" t="s">
+        <v>95</v>
+      </c>
+      <c r="E101" t="s">
+        <v>31</v>
+      </c>
+      <c r="F101" s="2">
+        <v>46064</v>
+      </c>
+      <c r="G101" t="s">
+        <v>96</v>
+      </c>
+      <c r="H101" t="s">
+        <v>97</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>65</v>
+      </c>
+      <c r="K101" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>83</v>
+      </c>
+      <c r="B102" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C102" t="s">
+        <v>29</v>
+      </c>
+      <c r="D102" t="s">
+        <v>95</v>
+      </c>
+      <c r="E102" t="s">
+        <v>31</v>
+      </c>
+      <c r="F102" s="2">
+        <v>46064</v>
+      </c>
+      <c r="G102" t="s">
+        <v>96</v>
+      </c>
+      <c r="H102" t="s">
+        <v>97</v>
+      </c>
+      <c r="I102" t="s">
+        <v>1</v>
+      </c>
+      <c r="J102" t="s">
+        <v>6</v>
+      </c>
+      <c r="K102" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>83</v>
+      </c>
+      <c r="B103" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C103" t="s">
+        <v>29</v>
+      </c>
+      <c r="D103" t="s">
+        <v>98</v>
+      </c>
+      <c r="E103" t="s">
+        <v>31</v>
+      </c>
+      <c r="F103" s="2">
+        <v>46065</v>
+      </c>
+      <c r="G103" t="s">
+        <v>97</v>
+      </c>
+      <c r="H103" t="s">
+        <v>5</v>
+      </c>
+      <c r="I103" t="s">
+        <v>32</v>
+      </c>
+      <c r="J103" t="s">
+        <v>64</v>
+      </c>
+      <c r="K103" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>122</v>
+      </c>
+      <c r="B104" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C104" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
+        <v>98</v>
+      </c>
+      <c r="E104" t="s">
+        <v>4</v>
+      </c>
+      <c r="F104" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G104" t="s">
+        <v>110</v>
+      </c>
+      <c r="H104" t="s">
+        <v>108</v>
+      </c>
+      <c r="I104" t="s">
+        <v>32</v>
+      </c>
+      <c r="J104" t="s">
+        <v>64</v>
+      </c>
+      <c r="K104" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>83</v>
+      </c>
+      <c r="B105" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C105" t="s">
+        <v>29</v>
+      </c>
+      <c r="D105" t="s">
+        <v>98</v>
+      </c>
+      <c r="E105" t="s">
+        <v>31</v>
+      </c>
+      <c r="F105" s="2">
+        <v>46065</v>
+      </c>
+      <c r="G105" t="s">
+        <v>97</v>
+      </c>
+      <c r="H105" t="s">
+        <v>5</v>
+      </c>
+      <c r="I105" t="s">
+        <v>101</v>
+      </c>
+      <c r="J105" t="s">
+        <v>102</v>
+      </c>
+      <c r="K105" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>83</v>
+      </c>
+      <c r="B106" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C106" t="s">
+        <v>29</v>
+      </c>
+      <c r="D106" t="s">
+        <v>98</v>
+      </c>
+      <c r="E106" t="s">
+        <v>31</v>
+      </c>
+      <c r="F106" s="2">
+        <v>46065</v>
+      </c>
+      <c r="G106" t="s">
+        <v>97</v>
+      </c>
+      <c r="H106" t="s">
+        <v>5</v>
+      </c>
+      <c r="I106" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s">
+        <v>65</v>
+      </c>
+      <c r="K106" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>83</v>
+      </c>
+      <c r="B107" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C107" t="s">
+        <v>29</v>
+      </c>
+      <c r="D107" t="s">
+        <v>98</v>
+      </c>
+      <c r="E107" t="s">
+        <v>31</v>
+      </c>
+      <c r="F107" s="2">
+        <v>46065</v>
+      </c>
+      <c r="G107" t="s">
+        <v>97</v>
+      </c>
+      <c r="H107" t="s">
+        <v>5</v>
+      </c>
+      <c r="I107" t="s">
+        <v>43</v>
+      </c>
+      <c r="J107" t="s">
+        <v>44</v>
+      </c>
+      <c r="K107" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>122</v>
+      </c>
+      <c r="B108" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C108" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
+        <v>98</v>
+      </c>
+      <c r="E108" t="s">
+        <v>4</v>
+      </c>
+      <c r="F108" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G108" t="s">
+        <v>110</v>
+      </c>
+      <c r="H108" t="s">
+        <v>108</v>
+      </c>
+      <c r="I108" t="s">
+        <v>13</v>
+      </c>
+      <c r="J108" t="s">
+        <v>65</v>
+      </c>
+      <c r="K108" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>83</v>
+      </c>
+      <c r="B109" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C109" t="s">
+        <v>29</v>
+      </c>
+      <c r="D109" t="s">
+        <v>98</v>
+      </c>
+      <c r="E109" t="s">
+        <v>31</v>
+      </c>
+      <c r="F109" s="2">
+        <v>46065</v>
+      </c>
+      <c r="G109" t="s">
+        <v>97</v>
+      </c>
+      <c r="H109" t="s">
+        <v>5</v>
+      </c>
+      <c r="I109" t="s">
+        <v>99</v>
+      </c>
+      <c r="J109" t="s">
+        <v>100</v>
+      </c>
+      <c r="K109" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>122</v>
+      </c>
+      <c r="B110" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>98</v>
+      </c>
+      <c r="E110" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G110" t="s">
+        <v>110</v>
+      </c>
+      <c r="H110" t="s">
+        <v>108</v>
+      </c>
+      <c r="I110" t="s">
+        <v>123</v>
+      </c>
+      <c r="J110" t="s">
+        <v>124</v>
+      </c>
+      <c r="K110" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>122</v>
+      </c>
+      <c r="B111" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>98</v>
+      </c>
+      <c r="E111" t="s">
+        <v>4</v>
+      </c>
+      <c r="F111" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G111" t="s">
+        <v>110</v>
+      </c>
+      <c r="H111" t="s">
+        <v>108</v>
+      </c>
+      <c r="I111" t="s">
+        <v>16</v>
+      </c>
+      <c r="J111" t="s">
+        <v>141</v>
+      </c>
+      <c r="K111" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>83</v>
+      </c>
+      <c r="B112" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="C112" t="s">
+        <v>29</v>
+      </c>
+      <c r="D112" t="s">
+        <v>98</v>
+      </c>
+      <c r="E112" t="s">
+        <v>31</v>
+      </c>
+      <c r="F112" s="2">
+        <v>46065</v>
+      </c>
+      <c r="G112" t="s">
+        <v>97</v>
+      </c>
+      <c r="H112" t="s">
+        <v>5</v>
+      </c>
+      <c r="I112" t="s">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>6</v>
+      </c>
+      <c r="K112" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>98</v>
+      </c>
+      <c r="E113" t="s">
+        <v>4</v>
+      </c>
+      <c r="F113" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G113" t="s">
+        <v>110</v>
+      </c>
+      <c r="H113" t="s">
+        <v>108</v>
+      </c>
+      <c r="I113" t="s">
+        <v>1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>6</v>
+      </c>
+      <c r="K113" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="1">
+        <v>1.2500000000000001E-2</v>
+      </c>
+      <c r="C114" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>98</v>
+      </c>
+      <c r="E114" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G114" t="s">
+        <v>110</v>
+      </c>
+      <c r="H114" t="s">
+        <v>108</v>
+      </c>
+      <c r="I114" t="s">
+        <v>125</v>
+      </c>
+      <c r="J114" t="s">
+        <v>126</v>
+      </c>
+      <c r="K114" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>103</v>
+      </c>
+      <c r="B115" s="1">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C115" t="s">
+        <v>17</v>
+      </c>
+      <c r="D115" t="s">
+        <v>104</v>
+      </c>
+      <c r="E115" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G115" t="s">
+        <v>5</v>
+      </c>
+      <c r="H115" t="s">
+        <v>105</v>
+      </c>
+      <c r="I115" t="s">
+        <v>32</v>
+      </c>
+      <c r="J115" t="s">
+        <v>64</v>
+      </c>
+      <c r="K115" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>103</v>
+      </c>
+      <c r="B116" s="1">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C116" t="s">
+        <v>17</v>
+      </c>
+      <c r="D116" t="s">
+        <v>104</v>
+      </c>
+      <c r="E116" t="s">
+        <v>4</v>
+      </c>
+      <c r="F116" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G116" t="s">
+        <v>5</v>
+      </c>
+      <c r="H116" t="s">
+        <v>105</v>
+      </c>
+      <c r="I116" t="s">
+        <v>22</v>
+      </c>
+      <c r="J116" t="s">
+        <v>62</v>
+      </c>
+      <c r="K116" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>103</v>
+      </c>
+      <c r="B117" s="1">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C117" t="s">
+        <v>17</v>
+      </c>
+      <c r="D117" t="s">
+        <v>104</v>
+      </c>
+      <c r="E117" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G117" t="s">
+        <v>5</v>
+      </c>
+      <c r="H117" t="s">
+        <v>105</v>
+      </c>
+      <c r="I117" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" t="s">
+        <v>65</v>
+      </c>
+      <c r="K117" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>103</v>
+      </c>
+      <c r="B118" s="1">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C118" t="s">
+        <v>17</v>
+      </c>
+      <c r="D118" t="s">
+        <v>104</v>
+      </c>
+      <c r="E118" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G118" t="s">
+        <v>5</v>
+      </c>
+      <c r="H118" t="s">
+        <v>105</v>
+      </c>
+      <c r="I118" t="s">
+        <v>106</v>
+      </c>
+      <c r="J118" t="s">
+        <v>136</v>
+      </c>
+      <c r="K118" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>103</v>
+      </c>
+      <c r="B119" s="1">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C119" t="s">
+        <v>17</v>
+      </c>
+      <c r="D119" t="s">
+        <v>104</v>
+      </c>
+      <c r="E119" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G119" t="s">
+        <v>5</v>
+      </c>
+      <c r="H119" t="s">
+        <v>105</v>
+      </c>
+      <c r="I119" t="s">
+        <v>26</v>
+      </c>
+      <c r="J119" t="s">
+        <v>27</v>
+      </c>
+      <c r="K119" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>103</v>
+      </c>
+      <c r="B120" s="1">
+        <v>4.8611111111111112E-2</v>
+      </c>
+      <c r="C120" t="s">
+        <v>17</v>
+      </c>
+      <c r="D120" t="s">
+        <v>104</v>
+      </c>
+      <c r="E120" t="s">
+        <v>4</v>
+      </c>
+      <c r="F120" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G120" t="s">
+        <v>5</v>
+      </c>
+      <c r="H120" t="s">
+        <v>105</v>
+      </c>
+      <c r="I120" t="s">
+        <v>1</v>
+      </c>
+      <c r="J120" t="s">
+        <v>6</v>
+      </c>
+      <c r="K120" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>103</v>
+      </c>
+      <c r="B121" s="1">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="C121" t="s">
+        <v>17</v>
+      </c>
+      <c r="D121" t="s">
+        <v>107</v>
+      </c>
+      <c r="E121" t="s">
+        <v>4</v>
+      </c>
+      <c r="F121" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G121" t="s">
+        <v>75</v>
+      </c>
+      <c r="H121" t="s">
+        <v>108</v>
+      </c>
+      <c r="I121" t="s">
+        <v>32</v>
+      </c>
+      <c r="J121" t="s">
+        <v>64</v>
+      </c>
+      <c r="K121" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>103</v>
+      </c>
+      <c r="B122" s="1">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="C122" t="s">
+        <v>17</v>
+      </c>
+      <c r="D122" t="s">
+        <v>107</v>
+      </c>
+      <c r="E122" t="s">
+        <v>4</v>
+      </c>
+      <c r="F122" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G122" t="s">
+        <v>75</v>
+      </c>
+      <c r="H122" t="s">
+        <v>108</v>
+      </c>
+      <c r="I122" t="s">
+        <v>22</v>
+      </c>
+      <c r="J122" t="s">
+        <v>62</v>
+      </c>
+      <c r="K122" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>103</v>
+      </c>
+      <c r="B123" s="1">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="C123" t="s">
+        <v>17</v>
+      </c>
+      <c r="D123" t="s">
+        <v>107</v>
+      </c>
+      <c r="E123" t="s">
+        <v>4</v>
+      </c>
+      <c r="F123" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G123" t="s">
+        <v>75</v>
+      </c>
+      <c r="H123" t="s">
+        <v>108</v>
+      </c>
+      <c r="I123" t="s">
+        <v>13</v>
+      </c>
+      <c r="J123" t="s">
+        <v>65</v>
+      </c>
+      <c r="K123" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>103</v>
+      </c>
+      <c r="B124" s="1">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="C124" t="s">
+        <v>17</v>
+      </c>
+      <c r="D124" t="s">
+        <v>107</v>
+      </c>
+      <c r="E124" t="s">
+        <v>4</v>
+      </c>
+      <c r="F124" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G124" t="s">
+        <v>75</v>
+      </c>
+      <c r="H124" t="s">
+        <v>108</v>
+      </c>
+      <c r="I124" t="s">
+        <v>99</v>
+      </c>
+      <c r="J124" t="s">
+        <v>100</v>
+      </c>
+      <c r="K124" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>103</v>
+      </c>
+      <c r="B125" s="1">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="C125" t="s">
+        <v>17</v>
+      </c>
+      <c r="D125" t="s">
+        <v>107</v>
+      </c>
+      <c r="E125" t="s">
+        <v>4</v>
+      </c>
+      <c r="F125" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G125" t="s">
+        <v>75</v>
+      </c>
+      <c r="H125" t="s">
+        <v>108</v>
+      </c>
+      <c r="I125" t="s">
+        <v>26</v>
+      </c>
+      <c r="J125" t="s">
+        <v>27</v>
+      </c>
+      <c r="K125" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>103</v>
+      </c>
+      <c r="B126" s="1">
+        <v>7.9166666666666663E-2</v>
+      </c>
+      <c r="C126" t="s">
+        <v>17</v>
+      </c>
+      <c r="D126" t="s">
+        <v>107</v>
+      </c>
+      <c r="E126" t="s">
+        <v>4</v>
+      </c>
+      <c r="F126" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G126" t="s">
+        <v>75</v>
+      </c>
+      <c r="H126" t="s">
+        <v>108</v>
+      </c>
+      <c r="I126" t="s">
+        <v>1</v>
+      </c>
+      <c r="J126" t="s">
+        <v>6</v>
+      </c>
+      <c r="K126" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>103</v>
+      </c>
+      <c r="B127" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C127" t="s">
+        <v>17</v>
+      </c>
+      <c r="D127" t="s">
+        <v>109</v>
+      </c>
+      <c r="E127" t="s">
+        <v>4</v>
+      </c>
+      <c r="F127" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G127" t="s">
+        <v>110</v>
+      </c>
+      <c r="H127" t="s">
+        <v>5</v>
+      </c>
+      <c r="I127" t="s">
+        <v>32</v>
+      </c>
+      <c r="J127" t="s">
+        <v>64</v>
+      </c>
+      <c r="K127" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>103</v>
+      </c>
+      <c r="B128" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C128" t="s">
+        <v>17</v>
+      </c>
+      <c r="D128" t="s">
+        <v>109</v>
+      </c>
+      <c r="E128" t="s">
+        <v>4</v>
+      </c>
+      <c r="F128" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G128" t="s">
+        <v>110</v>
+      </c>
+      <c r="H128" t="s">
+        <v>5</v>
+      </c>
+      <c r="I128" t="s">
+        <v>22</v>
+      </c>
+      <c r="J128" t="s">
+        <v>62</v>
+      </c>
+      <c r="K128" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>103</v>
+      </c>
+      <c r="B129" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C129" t="s">
+        <v>17</v>
+      </c>
+      <c r="D129" t="s">
+        <v>109</v>
+      </c>
+      <c r="E129" t="s">
+        <v>4</v>
+      </c>
+      <c r="F129" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G129" t="s">
+        <v>110</v>
+      </c>
+      <c r="H129" t="s">
+        <v>5</v>
+      </c>
+      <c r="I129" t="s">
+        <v>114</v>
+      </c>
+      <c r="J129" t="s">
+        <v>115</v>
+      </c>
+      <c r="K129" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>103</v>
+      </c>
+      <c r="B130" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C130" t="s">
+        <v>17</v>
+      </c>
+      <c r="D130" t="s">
+        <v>109</v>
+      </c>
+      <c r="E130" t="s">
+        <v>4</v>
+      </c>
+      <c r="F130" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G130" t="s">
+        <v>110</v>
+      </c>
+      <c r="H130" t="s">
+        <v>5</v>
+      </c>
+      <c r="I130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" t="s">
+        <v>65</v>
+      </c>
+      <c r="K130" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>103</v>
+      </c>
+      <c r="B131" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C131" t="s">
+        <v>17</v>
+      </c>
+      <c r="D131" t="s">
+        <v>109</v>
+      </c>
+      <c r="E131" t="s">
+        <v>4</v>
+      </c>
+      <c r="F131" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G131" t="s">
+        <v>110</v>
+      </c>
+      <c r="H131" t="s">
+        <v>5</v>
+      </c>
+      <c r="I131" t="s">
+        <v>111</v>
+      </c>
+      <c r="J131" t="s">
+        <v>142</v>
+      </c>
+      <c r="K131" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>103</v>
+      </c>
+      <c r="B132" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C132" t="s">
+        <v>17</v>
+      </c>
+      <c r="D132" t="s">
+        <v>109</v>
+      </c>
+      <c r="E132" t="s">
+        <v>4</v>
+      </c>
+      <c r="F132" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G132" t="s">
+        <v>110</v>
+      </c>
+      <c r="H132" t="s">
+        <v>5</v>
+      </c>
+      <c r="I132" t="s">
+        <v>113</v>
+      </c>
+      <c r="J132" t="s">
+        <v>100</v>
+      </c>
+      <c r="K132" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>103</v>
+      </c>
+      <c r="B133" s="1">
+        <v>2.9166666666666667E-2</v>
+      </c>
+      <c r="C133" t="s">
+        <v>17</v>
+      </c>
+      <c r="D133" t="s">
+        <v>109</v>
+      </c>
+      <c r="E133" t="s">
+        <v>4</v>
+      </c>
+      <c r="F133" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G133" t="s">
+        <v>110</v>
+      </c>
+      <c r="H133" t="s">
+        <v>5</v>
+      </c>
+      <c r="I133" t="s">
+        <v>1</v>
+      </c>
+      <c r="J133" t="s">
+        <v>6</v>
+      </c>
+      <c r="K133" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>127</v>
+      </c>
+      <c r="B134" s="1">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C134" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" t="s">
+        <v>128</v>
+      </c>
+      <c r="E134" t="s">
+        <v>4</v>
+      </c>
+      <c r="F134" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G134" t="s">
+        <v>5</v>
+      </c>
+      <c r="H134" t="s">
+        <v>49</v>
+      </c>
+      <c r="I134" t="s">
+        <v>32</v>
+      </c>
+      <c r="J134" t="s">
+        <v>64</v>
+      </c>
+      <c r="K134" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>127</v>
+      </c>
+      <c r="B135" s="1">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C135" t="s">
+        <v>17</v>
+      </c>
+      <c r="D135" t="s">
+        <v>128</v>
+      </c>
+      <c r="E135" t="s">
+        <v>4</v>
+      </c>
+      <c r="F135" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G135" t="s">
+        <v>5</v>
+      </c>
+      <c r="H135" t="s">
+        <v>49</v>
+      </c>
+      <c r="I135" t="s">
+        <v>129</v>
+      </c>
+      <c r="J135" t="s">
+        <v>135</v>
+      </c>
+      <c r="K135" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>127</v>
+      </c>
+      <c r="B136" s="1">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C136" t="s">
+        <v>17</v>
+      </c>
+      <c r="D136" t="s">
+        <v>128</v>
+      </c>
+      <c r="E136" t="s">
+        <v>4</v>
+      </c>
+      <c r="F136" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G136" t="s">
+        <v>5</v>
+      </c>
+      <c r="H136" t="s">
+        <v>49</v>
+      </c>
+      <c r="I136" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" t="s">
+        <v>44</v>
+      </c>
+      <c r="K136" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>127</v>
+      </c>
+      <c r="B137" s="1">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C137" t="s">
+        <v>17</v>
+      </c>
+      <c r="D137" t="s">
+        <v>128</v>
+      </c>
+      <c r="E137" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G137" t="s">
+        <v>5</v>
+      </c>
+      <c r="H137" t="s">
+        <v>49</v>
+      </c>
+      <c r="I137" t="s">
+        <v>13</v>
+      </c>
+      <c r="J137" t="s">
+        <v>65</v>
+      </c>
+      <c r="K137" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>127</v>
+      </c>
+      <c r="B138" s="1">
+        <v>3.7499999999999999E-2</v>
+      </c>
+      <c r="C138" t="s">
+        <v>17</v>
+      </c>
+      <c r="D138" t="s">
+        <v>128</v>
+      </c>
+      <c r="E138" t="s">
+        <v>4</v>
+      </c>
+      <c r="F138" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G138" t="s">
+        <v>5</v>
+      </c>
+      <c r="H138" t="s">
+        <v>49</v>
+      </c>
+      <c r="I138" t="s">
+        <v>1</v>
+      </c>
+      <c r="J138" t="s">
+        <v>6</v>
+      </c>
+      <c r="K138" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>127</v>
+      </c>
+      <c r="B139" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C139" t="s">
+        <v>17</v>
+      </c>
+      <c r="D139" t="s">
+        <v>130</v>
+      </c>
+      <c r="E139" t="s">
+        <v>4</v>
+      </c>
+      <c r="F139" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G139" t="s">
+        <v>49</v>
+      </c>
+      <c r="H139" t="s">
+        <v>110</v>
+      </c>
+      <c r="I139" t="s">
+        <v>32</v>
+      </c>
+      <c r="J139" t="s">
+        <v>64</v>
+      </c>
+      <c r="K139" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>127</v>
+      </c>
+      <c r="B140" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C140" t="s">
+        <v>17</v>
+      </c>
+      <c r="D140" t="s">
+        <v>130</v>
+      </c>
+      <c r="E140" t="s">
+        <v>4</v>
+      </c>
+      <c r="F140" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G140" t="s">
+        <v>49</v>
+      </c>
+      <c r="H140" t="s">
+        <v>110</v>
+      </c>
+      <c r="I140" t="s">
+        <v>13</v>
+      </c>
+      <c r="J140" t="s">
+        <v>65</v>
+      </c>
+      <c r="K140" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>127</v>
+      </c>
+      <c r="B141" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C141" t="s">
+        <v>17</v>
+      </c>
+      <c r="D141" t="s">
+        <v>130</v>
+      </c>
+      <c r="E141" t="s">
+        <v>4</v>
+      </c>
+      <c r="F141" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G141" t="s">
+        <v>49</v>
+      </c>
+      <c r="H141" t="s">
+        <v>110</v>
+      </c>
+      <c r="I141" t="s">
+        <v>1</v>
+      </c>
+      <c r="J141" t="s">
+        <v>6</v>
+      </c>
+      <c r="K141" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>127</v>
+      </c>
+      <c r="B142" s="1">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C142" t="s">
+        <v>17</v>
+      </c>
+      <c r="D142" t="s">
+        <v>130</v>
+      </c>
+      <c r="E142" t="s">
+        <v>4</v>
+      </c>
+      <c r="F142" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G142" t="s">
+        <v>49</v>
+      </c>
+      <c r="H142" t="s">
+        <v>110</v>
+      </c>
+      <c r="I142" t="s">
+        <v>125</v>
+      </c>
+      <c r="J142" t="s">
+        <v>131</v>
+      </c>
+      <c r="K142" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>127</v>
+      </c>
+      <c r="B143" s="1">
+        <v>4.583333333333333E-2</v>
+      </c>
+      <c r="C143" t="s">
+        <v>17</v>
+      </c>
+      <c r="D143" t="s">
+        <v>132</v>
+      </c>
+      <c r="E143" t="s">
+        <v>4</v>
+      </c>
+      <c r="F143" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G143" t="s">
+        <v>110</v>
+      </c>
+      <c r="H143" t="s">
+        <v>49</v>
+      </c>
+      <c r="I143" t="s">
+        <v>32</v>
+      </c>
+      <c r="J143" t="s">
+        <v>64</v>
+      </c>
+      <c r="K143" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>127</v>
+      </c>
+      <c r="B144" s="1">
+        <v>4.583333333333333E-2</v>
+      </c>
+      <c r="C144" t="s">
+        <v>17</v>
+      </c>
+      <c r="D144" t="s">
+        <v>132</v>
+      </c>
+      <c r="E144" t="s">
+        <v>4</v>
+      </c>
+      <c r="F144" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G144" t="s">
+        <v>110</v>
+      </c>
+      <c r="H144" t="s">
+        <v>49</v>
+      </c>
+      <c r="I144" t="s">
+        <v>13</v>
+      </c>
+      <c r="J144" t="s">
+        <v>65</v>
+      </c>
+      <c r="K144" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>127</v>
+      </c>
+      <c r="B145" s="1">
+        <v>4.583333333333333E-2</v>
+      </c>
+      <c r="C145" t="s">
+        <v>17</v>
+      </c>
+      <c r="D145" t="s">
+        <v>132</v>
+      </c>
+      <c r="E145" t="s">
+        <v>4</v>
+      </c>
+      <c r="F145" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G145" t="s">
+        <v>110</v>
+      </c>
+      <c r="H145" t="s">
+        <v>49</v>
+      </c>
+      <c r="I145" t="s">
+        <v>1</v>
+      </c>
+      <c r="J145" t="s">
+        <v>6</v>
+      </c>
+      <c r="K145" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>127</v>
+      </c>
+      <c r="B146" s="1">
+        <v>4.583333333333333E-2</v>
+      </c>
+      <c r="C146" t="s">
+        <v>17</v>
+      </c>
+      <c r="D146" t="s">
+        <v>132</v>
+      </c>
+      <c r="E146" t="s">
+        <v>4</v>
+      </c>
+      <c r="F146" s="2">
+        <v>46079</v>
+      </c>
+      <c r="G146" t="s">
+        <v>110</v>
+      </c>
+      <c r="H146" t="s">
+        <v>49</v>
+      </c>
+      <c r="I146" t="s">
+        <v>125</v>
+      </c>
+      <c r="J146" t="s">
+        <v>131</v>
+      </c>
+      <c r="K146" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>127</v>
+      </c>
+      <c r="B147" s="1">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="C147" t="s">
+        <v>17</v>
+      </c>
+      <c r="D147" t="s">
+        <v>133</v>
+      </c>
+      <c r="E147" t="s">
+        <v>4</v>
+      </c>
+      <c r="F147" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G147" t="s">
+        <v>49</v>
+      </c>
+      <c r="H147" t="s">
+        <v>5</v>
+      </c>
+      <c r="I147" t="s">
+        <v>32</v>
+      </c>
+      <c r="J147" t="s">
+        <v>64</v>
+      </c>
+      <c r="K147" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>127</v>
+      </c>
+      <c r="B148" s="1">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="C148" t="s">
+        <v>17</v>
+      </c>
+      <c r="D148" t="s">
+        <v>133</v>
+      </c>
+      <c r="E148" t="s">
+        <v>4</v>
+      </c>
+      <c r="F148" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G148" t="s">
+        <v>49</v>
+      </c>
+      <c r="H148" t="s">
+        <v>5</v>
+      </c>
+      <c r="I148" t="s">
+        <v>129</v>
+      </c>
+      <c r="J148" t="s">
+        <v>135</v>
+      </c>
+      <c r="K148" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>127</v>
+      </c>
+      <c r="B149" s="1">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="C149" t="s">
+        <v>17</v>
+      </c>
+      <c r="D149" t="s">
+        <v>133</v>
+      </c>
+      <c r="E149" t="s">
+        <v>4</v>
+      </c>
+      <c r="F149" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G149" t="s">
+        <v>49</v>
+      </c>
+      <c r="H149" t="s">
+        <v>5</v>
+      </c>
+      <c r="I149" t="s">
+        <v>43</v>
+      </c>
+      <c r="J149" t="s">
+        <v>44</v>
+      </c>
+      <c r="K149" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>127</v>
+      </c>
+      <c r="B150" s="1">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="C150" t="s">
+        <v>17</v>
+      </c>
+      <c r="D150" t="s">
+        <v>133</v>
+      </c>
+      <c r="E150" t="s">
+        <v>4</v>
+      </c>
+      <c r="F150" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G150" t="s">
+        <v>49</v>
+      </c>
+      <c r="H150" t="s">
+        <v>5</v>
+      </c>
+      <c r="I150" t="s">
+        <v>13</v>
+      </c>
+      <c r="J150" t="s">
+        <v>65</v>
+      </c>
+      <c r="K150" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>127</v>
+      </c>
+      <c r="B151" s="1">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="C151" t="s">
+        <v>17</v>
+      </c>
+      <c r="D151" t="s">
+        <v>133</v>
+      </c>
+      <c r="E151" t="s">
+        <v>4</v>
+      </c>
+      <c r="F151" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G151" t="s">
+        <v>49</v>
+      </c>
+      <c r="H151" t="s">
+        <v>5</v>
+      </c>
+      <c r="I151" t="s">
+        <v>1</v>
+      </c>
+      <c r="J151" t="s">
+        <v>6</v>
+      </c>
+      <c r="K151" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>127</v>
+      </c>
+      <c r="B152" s="1">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="C152" t="s">
+        <v>17</v>
+      </c>
+      <c r="D152" t="s">
+        <v>133</v>
+      </c>
+      <c r="E152" t="s">
+        <v>4</v>
+      </c>
+      <c r="F152" s="2">
+        <v>46080</v>
+      </c>
+      <c r="G152" t="s">
+        <v>49</v>
+      </c>
+      <c r="H152" t="s">
+        <v>5</v>
+      </c>
+      <c r="I152" t="s">
+        <v>125</v>
+      </c>
+      <c r="J152" t="s">
+        <v>131</v>
+      </c>
+      <c r="K152" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>119</v>
+      </c>
+      <c r="B153" s="1">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="C153" t="s">
+        <v>116</v>
+      </c>
+      <c r="D153" t="s">
+        <v>117</v>
+      </c>
+      <c r="E153" t="s">
+        <v>118</v>
+      </c>
+      <c r="F153" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G153" t="s">
+        <v>108</v>
+      </c>
+      <c r="H153" t="s">
+        <v>108</v>
+      </c>
+      <c r="I153" t="s">
+        <v>32</v>
+      </c>
+      <c r="J153" t="s">
+        <v>64</v>
+      </c>
+      <c r="K153" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>119</v>
+      </c>
+      <c r="B154" s="1">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="C154" t="s">
+        <v>116</v>
+      </c>
+      <c r="D154" t="s">
+        <v>117</v>
+      </c>
+      <c r="E154" t="s">
+        <v>118</v>
+      </c>
+      <c r="F154" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G154" t="s">
+        <v>108</v>
+      </c>
+      <c r="H154" t="s">
+        <v>108</v>
+      </c>
+      <c r="I154" t="s">
+        <v>111</v>
+      </c>
+      <c r="J154" t="s">
+        <v>142</v>
+      </c>
+      <c r="K154" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>119</v>
+      </c>
+      <c r="B155" s="1">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="C155" t="s">
+        <v>116</v>
+      </c>
+      <c r="D155" t="s">
+        <v>117</v>
+      </c>
+      <c r="E155" t="s">
+        <v>118</v>
+      </c>
+      <c r="F155" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G155" t="s">
+        <v>108</v>
+      </c>
+      <c r="H155" t="s">
+        <v>108</v>
+      </c>
+      <c r="I155" t="s">
+        <v>16</v>
+      </c>
+      <c r="J155" t="s">
+        <v>141</v>
+      </c>
+      <c r="K155" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>119</v>
+      </c>
+      <c r="B156" s="1">
+        <v>1.6666666666666666E-2</v>
+      </c>
+      <c r="C156" t="s">
+        <v>116</v>
+      </c>
+      <c r="D156" t="s">
+        <v>117</v>
+      </c>
+      <c r="E156" t="s">
+        <v>118</v>
+      </c>
+      <c r="F156" s="2">
+        <v>46078</v>
+      </c>
+      <c r="G156" t="s">
+        <v>108</v>
+      </c>
+      <c r="H156" t="s">
+        <v>108</v>
+      </c>
+      <c r="I156" t="s">
+        <v>1</v>
+      </c>
+      <c r="J156" t="s">
+        <v>6</v>
+      </c>
+      <c r="K156" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:K1" xr:uid="{46D67731-6C8F-4D19-B5E9-3D6FBC4AC40F}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K51">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K156">
       <sortCondition ref="D1"/>
     </sortState>
   </autoFilter>

--- a/upload/voos_2026.xlsx
+++ b/upload/voos_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kbomf\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210AA7C6-64E3-47B4-961D-BD066ACFC8FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DA1E00-3DB0-45E2-952F-F5D700A793B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2566" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2450" uniqueCount="209">
   <si>
     <t>Traslado do Exmo. Governador de Minas e Comitiva até as cidades de São Antônio do Monte e Serra da Saudade/MG</t>
   </si>
@@ -473,9 +473,6 @@
     <t>0044-2026</t>
   </si>
   <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
     <t>Barbara Barros Botega</t>
   </si>
   <si>
@@ -488,9 +485,6 @@
     <t>0073-2026</t>
   </si>
   <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
     <t>SETE LAGOAS</t>
   </si>
   <si>
@@ -509,9 +503,6 @@
     <t>0049-2026</t>
   </si>
   <si>
-    <t>16/03/2026</t>
-  </si>
-  <si>
     <t>LAVRAS</t>
   </si>
   <si>
@@ -542,9 +533,6 @@
     <t>0052-2026</t>
   </si>
   <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
     <t>0053-2026</t>
   </si>
   <si>
@@ -554,9 +542,6 @@
     <t>PR-DTG</t>
   </si>
   <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
     <t>CIPOTÂNEA</t>
   </si>
   <si>
@@ -608,9 +593,6 @@
     <t>0061-2026</t>
   </si>
   <si>
-    <t>28/03/2026</t>
-  </si>
-  <si>
     <t>PATROCINIO</t>
   </si>
   <si>
@@ -626,9 +608,6 @@
     <t>0063-2026</t>
   </si>
   <si>
-    <t>29/03/2026</t>
-  </si>
-  <si>
     <t>Edimar Ferreira</t>
   </si>
   <si>
@@ -638,9 +617,6 @@
     <t>0064-2026</t>
   </si>
   <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
     <t>Não Informado</t>
   </si>
   <si>
@@ -651,9 +627,6 @@
   </si>
   <si>
     <t>2ª BRAvE</t>
-  </si>
-  <si>
-    <t>27/03/2026</t>
   </si>
   <si>
     <t>COROMANDEL</t>
@@ -4808,7 +4781,7 @@
         <v>101</v>
       </c>
       <c r="J94" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="K94" t="s">
         <v>42</v>
@@ -7000,8 +6973,8 @@
       <c r="E157" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F157" s="2" t="s">
-        <v>145</v>
+      <c r="F157" s="2">
+        <v>46090</v>
       </c>
       <c r="G157" s="3" t="s">
         <v>5</v>
@@ -7035,8 +7008,8 @@
       <c r="E158" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F158" s="2" t="s">
-        <v>145</v>
+      <c r="F158" s="2">
+        <v>46090</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>75</v>
@@ -7070,8 +7043,8 @@
       <c r="E159" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F159" s="2" t="s">
-        <v>145</v>
+      <c r="F159" s="2">
+        <v>46090</v>
       </c>
       <c r="G159" s="3" t="s">
         <v>5</v>
@@ -7105,8 +7078,8 @@
       <c r="E160" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F160" s="2" t="s">
-        <v>145</v>
+      <c r="F160" s="2">
+        <v>46090</v>
       </c>
       <c r="G160" s="3" t="s">
         <v>75</v>
@@ -7140,8 +7113,8 @@
       <c r="E161" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F161" s="2" t="s">
-        <v>145</v>
+      <c r="F161" s="2">
+        <v>46090</v>
       </c>
       <c r="G161" s="3" t="s">
         <v>5</v>
@@ -7175,8 +7148,8 @@
       <c r="E162" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F162" s="2" t="s">
-        <v>145</v>
+      <c r="F162" s="2">
+        <v>46090</v>
       </c>
       <c r="G162" s="3" t="s">
         <v>75</v>
@@ -7210,8 +7183,8 @@
       <c r="E163" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F163" s="2" t="s">
-        <v>145</v>
+      <c r="F163" s="2">
+        <v>46090</v>
       </c>
       <c r="G163" s="3" t="s">
         <v>5</v>
@@ -7245,8 +7218,8 @@
       <c r="E164" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F164" s="2" t="s">
-        <v>145</v>
+      <c r="F164" s="2">
+        <v>46090</v>
       </c>
       <c r="G164" s="3" t="s">
         <v>75</v>
@@ -7280,8 +7253,8 @@
       <c r="E165" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F165" s="2" t="s">
-        <v>145</v>
+      <c r="F165" s="2">
+        <v>46090</v>
       </c>
       <c r="G165" s="3" t="s">
         <v>5</v>
@@ -7315,8 +7288,8 @@
       <c r="E166" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F166" s="2" t="s">
-        <v>145</v>
+      <c r="F166" s="2">
+        <v>46090</v>
       </c>
       <c r="G166" s="3" t="s">
         <v>75</v>
@@ -7350,8 +7323,8 @@
       <c r="E167" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F167" s="2" t="s">
-        <v>145</v>
+      <c r="F167" s="2">
+        <v>46090</v>
       </c>
       <c r="G167" s="3" t="s">
         <v>5</v>
@@ -7385,8 +7358,8 @@
       <c r="E168" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F168" s="2" t="s">
-        <v>145</v>
+      <c r="F168" s="2">
+        <v>46090</v>
       </c>
       <c r="G168" s="3" t="s">
         <v>75</v>
@@ -7420,8 +7393,8 @@
       <c r="E169" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F169" s="2" t="s">
-        <v>145</v>
+      <c r="F169" s="2">
+        <v>46090</v>
       </c>
       <c r="G169" s="3" t="s">
         <v>5</v>
@@ -7430,13 +7403,13 @@
         <v>75</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J169" t="s">
         <v>62</v>
       </c>
       <c r="K169" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -7455,8 +7428,8 @@
       <c r="E170" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F170" s="2" t="s">
-        <v>145</v>
+      <c r="F170" s="2">
+        <v>46090</v>
       </c>
       <c r="G170" s="3" t="s">
         <v>75</v>
@@ -7465,39 +7438,39 @@
         <v>5</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J170" t="s">
         <v>62</v>
       </c>
       <c r="K170" s="3" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B171" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C171" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E171" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F171" s="2" t="s">
-        <v>150</v>
+      <c r="F171" s="2">
+        <v>46092</v>
       </c>
       <c r="G171" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I171" s="3" t="s">
         <v>32</v>
@@ -7511,25 +7484,25 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B172" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E172" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F172" s="2" t="s">
-        <v>150</v>
+      <c r="F172" s="2">
+        <v>46092</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H172" s="3" t="s">
         <v>5</v>
@@ -7546,28 +7519,28 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B173" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C173" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D173" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D173" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E173" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F173" s="2" t="s">
-        <v>150</v>
+      <c r="F173" s="2">
+        <v>46092</v>
       </c>
       <c r="G173" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I173" s="3" t="s">
         <v>13</v>
@@ -7581,25 +7554,25 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B174" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E174" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F174" s="2" t="s">
-        <v>150</v>
+      <c r="F174" s="2">
+        <v>46092</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H174" s="3" t="s">
         <v>5</v>
@@ -7616,25 +7589,25 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B175" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E175" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F175" s="2" t="s">
-        <v>150</v>
+      <c r="F175" s="2">
+        <v>46092</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H175" s="3" t="s">
         <v>5</v>
@@ -7651,28 +7624,28 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B176" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C176" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D176" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D176" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E176" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F176" s="2" t="s">
-        <v>150</v>
+      <c r="F176" s="2">
+        <v>46092</v>
       </c>
       <c r="G176" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I176" s="3" t="s">
         <v>128</v>
@@ -7686,28 +7659,28 @@
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B177" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C177" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D177" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D177" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E177" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F177" s="2" t="s">
-        <v>150</v>
+      <c r="F177" s="2">
+        <v>46092</v>
       </c>
       <c r="G177" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I177" s="3" t="s">
         <v>33</v>
@@ -7716,30 +7689,30 @@
         <v>62</v>
       </c>
       <c r="K177" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B178" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E178" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F178" s="2" t="s">
-        <v>150</v>
+      <c r="F178" s="2">
+        <v>46092</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H178" s="3" t="s">
         <v>5</v>
@@ -7756,28 +7729,28 @@
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B179" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C179" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>149</v>
       </c>
       <c r="E179" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F179" s="2" t="s">
-        <v>150</v>
+      <c r="F179" s="2">
+        <v>46092</v>
       </c>
       <c r="G179" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>1</v>
@@ -7791,25 +7764,25 @@
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B180" s="4">
         <v>2.9166666666666667E-2</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E180" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F180" s="2" t="s">
-        <v>150</v>
+      <c r="F180" s="2">
+        <v>46092</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H180" s="3" t="s">
         <v>5</v>
@@ -7821,12 +7794,12 @@
         <v>62</v>
       </c>
       <c r="K180" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B181" s="4">
         <v>2.5000000000000001E-2</v>
@@ -7835,19 +7808,19 @@
         <v>143</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E181" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F181" s="2" t="s">
-        <v>157</v>
+      <c r="F181" s="2">
+        <v>46097</v>
       </c>
       <c r="G181" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I181" s="3" t="s">
         <v>7</v>
@@ -7861,7 +7834,7 @@
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B182" s="4">
         <v>1.6666666666666666E-2</v>
@@ -7870,19 +7843,19 @@
         <v>143</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E182" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F182" s="2" t="s">
-        <v>157</v>
+      <c r="F182" s="2">
+        <v>46098</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I182" s="3" t="s">
         <v>7</v>
@@ -7896,7 +7869,7 @@
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B183" s="4">
         <v>1.6666666666666666E-2</v>
@@ -7905,19 +7878,19 @@
         <v>143</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E183" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F183" s="2" t="s">
-        <v>157</v>
+      <c r="F183" s="2">
+        <v>46099</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I183" s="3" t="s">
         <v>128</v>
@@ -7931,7 +7904,7 @@
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B184" s="4">
         <v>2.5000000000000001E-2</v>
@@ -7940,19 +7913,19 @@
         <v>143</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E184" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F184" s="2" t="s">
-        <v>157</v>
+      <c r="F184" s="2">
+        <v>46100</v>
       </c>
       <c r="G184" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I184" s="3" t="s">
         <v>1</v>
@@ -7966,7 +7939,7 @@
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B185" s="4">
         <v>1.6666666666666666E-2</v>
@@ -7975,19 +7948,19 @@
         <v>143</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E185" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F185" s="2" t="s">
-        <v>157</v>
+      <c r="F185" s="2">
+        <v>46101</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>1</v>
@@ -8001,7 +7974,7 @@
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B186" s="4">
         <v>0.05</v>
@@ -8010,19 +7983,19 @@
         <v>143</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E186" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F186" s="2" t="s">
-        <v>157</v>
+      <c r="F186" s="2">
+        <v>46102</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>1</v>
@@ -8036,7 +8009,7 @@
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B187" s="4">
         <v>2.5000000000000001E-2</v>
@@ -8045,19 +8018,19 @@
         <v>143</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E187" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F187" s="2" t="s">
-        <v>157</v>
+      <c r="F187" s="2">
+        <v>46103</v>
       </c>
       <c r="G187" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>21</v>
@@ -8071,7 +8044,7 @@
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B188" s="4">
         <v>1.6666666666666666E-2</v>
@@ -8080,19 +8053,19 @@
         <v>143</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E188" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F188" s="2" t="s">
-        <v>157</v>
+      <c r="F188" s="2">
+        <v>46104</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I188" s="3" t="s">
         <v>21</v>
@@ -8106,7 +8079,7 @@
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B189" s="4">
         <v>2.5000000000000001E-2</v>
@@ -8115,25 +8088,25 @@
         <v>143</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E189" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F189" s="2" t="s">
-        <v>157</v>
+      <c r="F189" s="2">
+        <v>46105</v>
       </c>
       <c r="G189" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H189" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I189" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I189" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J189" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K189" s="3" t="s">
         <v>73</v>
@@ -8141,7 +8114,7 @@
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B190" s="4">
         <v>1.6666666666666666E-2</v>
@@ -8150,25 +8123,25 @@
         <v>143</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E190" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F190" s="2" t="s">
-        <v>157</v>
+      <c r="F190" s="2">
+        <v>46106</v>
       </c>
       <c r="G190" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I190" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="H190" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I190" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="J190" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K190" s="3" t="s">
         <v>73</v>
@@ -8176,7 +8149,7 @@
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B191" s="4">
         <v>2.5000000000000001E-2</v>
@@ -8185,33 +8158,33 @@
         <v>143</v>
       </c>
       <c r="D191" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E191" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F191" s="2">
+        <v>46107</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="I191" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E191" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F191" s="2" t="s">
+      <c r="J191" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G191" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H191" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="I191" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J191" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="K191" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B192" s="4">
         <v>1.6666666666666666E-2</v>
@@ -8220,33 +8193,33 @@
         <v>143</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E192" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F192" s="2" t="s">
+      <c r="F192" s="2">
+        <v>46108</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J192" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G192" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H192" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I192" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J192" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="K192" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B193" s="4">
         <v>2.5000000000000001E-2</v>
@@ -8255,19 +8228,19 @@
         <v>143</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E193" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F193" s="2" t="s">
-        <v>157</v>
+      <c r="F193" s="2">
+        <v>46109</v>
       </c>
       <c r="G193" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="I193" s="3" t="s">
         <v>33</v>
@@ -8276,12 +8249,12 @@
         <v>62</v>
       </c>
       <c r="K193" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B194" s="4">
         <v>1.6666666666666666E-2</v>
@@ -8290,19 +8263,19 @@
         <v>143</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E194" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F194" s="2" t="s">
-        <v>157</v>
+      <c r="F194" s="2">
+        <v>46110</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="I194" s="3" t="s">
         <v>33</v>
@@ -8311,12 +8284,12 @@
         <v>62</v>
       </c>
       <c r="K194" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B195" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8325,16 +8298,16 @@
         <v>143</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E195" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F195" s="2" t="s">
-        <v>168</v>
+      <c r="F195" s="2">
+        <v>46098</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H195" s="3" t="s">
         <v>19</v>
@@ -8351,7 +8324,7 @@
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B196" s="4">
         <v>0.05</v>
@@ -8360,13 +8333,13 @@
         <v>143</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E196" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F196" s="2" t="s">
-        <v>168</v>
+      <c r="F196" s="2">
+        <v>46098</v>
       </c>
       <c r="G196" s="3" t="s">
         <v>19</v>
@@ -8386,7 +8359,7 @@
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B197" s="4">
         <v>0.05</v>
@@ -8395,13 +8368,13 @@
         <v>143</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E197" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F197" s="2" t="s">
-        <v>168</v>
+      <c r="F197" s="2">
+        <v>46098</v>
       </c>
       <c r="G197" s="3" t="s">
         <v>19</v>
@@ -8421,7 +8394,7 @@
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B198" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8430,16 +8403,16 @@
         <v>143</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E198" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F198" s="2" t="s">
-        <v>168</v>
+      <c r="F198" s="2">
+        <v>46098</v>
       </c>
       <c r="G198" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H198" s="3" t="s">
         <v>19</v>
@@ -8456,7 +8429,7 @@
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B199" s="4">
         <v>0.05</v>
@@ -8465,13 +8438,13 @@
         <v>143</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E199" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F199" s="2" t="s">
-        <v>168</v>
+      <c r="F199" s="2">
+        <v>46098</v>
       </c>
       <c r="G199" s="3" t="s">
         <v>19</v>
@@ -8491,7 +8464,7 @@
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B200" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8500,16 +8473,16 @@
         <v>143</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E200" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F200" s="2" t="s">
-        <v>168</v>
+      <c r="F200" s="2">
+        <v>46098</v>
       </c>
       <c r="G200" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H200" s="3" t="s">
         <v>19</v>
@@ -8526,7 +8499,7 @@
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B201" s="4">
         <v>0.05</v>
@@ -8535,13 +8508,13 @@
         <v>143</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E201" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F201" s="2" t="s">
-        <v>168</v>
+      <c r="F201" s="2">
+        <v>46098</v>
       </c>
       <c r="G201" s="3" t="s">
         <v>19</v>
@@ -8561,7 +8534,7 @@
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B202" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8570,16 +8543,16 @@
         <v>143</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E202" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F202" s="2" t="s">
-        <v>168</v>
+      <c r="F202" s="2">
+        <v>46098</v>
       </c>
       <c r="G202" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H202" s="3" t="s">
         <v>19</v>
@@ -8596,7 +8569,7 @@
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B203" s="4">
         <v>0.05</v>
@@ -8605,13 +8578,13 @@
         <v>143</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E203" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F203" s="2" t="s">
-        <v>168</v>
+      <c r="F203" s="2">
+        <v>46098</v>
       </c>
       <c r="G203" s="3" t="s">
         <v>19</v>
@@ -8631,7 +8604,7 @@
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B204" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8640,25 +8613,25 @@
         <v>143</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E204" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F204" s="2" t="s">
-        <v>168</v>
+      <c r="F204" s="2">
+        <v>46098</v>
       </c>
       <c r="G204" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H204" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J204" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K204" s="3" t="s">
         <v>73</v>
@@ -8666,7 +8639,7 @@
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B205" s="4">
         <v>0.05</v>
@@ -8675,13 +8648,13 @@
         <v>143</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E205" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F205" s="2" t="s">
-        <v>168</v>
+      <c r="F205" s="2">
+        <v>46098</v>
       </c>
       <c r="G205" s="3" t="s">
         <v>19</v>
@@ -8690,10 +8663,10 @@
         <v>5</v>
       </c>
       <c r="I205" s="3" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J205" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="K205" s="3" t="s">
         <v>73</v>
@@ -8701,7 +8674,7 @@
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B206" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8710,33 +8683,33 @@
         <v>143</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E206" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F206" s="2" t="s">
-        <v>168</v>
+      <c r="F206" s="2">
+        <v>46098</v>
       </c>
       <c r="G206" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H206" s="3" t="s">
         <v>19</v>
       </c>
       <c r="I206" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J206" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="K206" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B207" s="4">
         <v>3.3333333333333333E-2</v>
@@ -8745,16 +8718,16 @@
         <v>143</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E207" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F207" s="2" t="s">
-        <v>168</v>
+      <c r="F207" s="2">
+        <v>46098</v>
       </c>
       <c r="G207" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H207" s="3" t="s">
         <v>19</v>
@@ -8766,12 +8739,12 @@
         <v>62</v>
       </c>
       <c r="K207" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B208" s="4">
         <v>0.05</v>
@@ -8780,13 +8753,13 @@
         <v>143</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="E208" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F208" s="2" t="s">
-        <v>168</v>
+      <c r="F208" s="2">
+        <v>46098</v>
       </c>
       <c r="G208" s="3" t="s">
         <v>19</v>
@@ -8801,18 +8774,18 @@
         <v>62</v>
       </c>
       <c r="K208" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B209" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>131</v>
@@ -8820,20 +8793,20 @@
       <c r="E209" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F209" s="2" t="s">
-        <v>172</v>
+      <c r="F209" s="2">
+        <v>46106</v>
       </c>
       <c r="G209" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H209" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I209" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J209" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K209" t="s">
         <v>63</v>
@@ -8841,13 +8814,13 @@
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B210" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>132</v>
@@ -8855,20 +8828,20 @@
       <c r="E210" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F210" s="2" t="s">
-        <v>172</v>
+      <c r="F210" s="2">
+        <v>46106</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H210" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I210" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J210" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K210" t="s">
         <v>63</v>
@@ -8876,7 +8849,7 @@
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B211" s="4">
         <v>6.5277777777777782E-2</v>
@@ -8885,13 +8858,13 @@
         <v>143</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E211" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F211" s="2" t="s">
-        <v>172</v>
+      <c r="F211" s="2">
+        <v>46106</v>
       </c>
       <c r="G211" s="3" t="s">
         <v>5</v>
@@ -8900,10 +8873,10 @@
         <v>75</v>
       </c>
       <c r="I211" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J211" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K211" t="s">
         <v>63</v>
@@ -8911,7 +8884,7 @@
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B212" s="4">
         <v>3.7499999999999999E-2</v>
@@ -8920,13 +8893,13 @@
         <v>143</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E212" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F212" s="2" t="s">
-        <v>172</v>
+      <c r="F212" s="2">
+        <v>46106</v>
       </c>
       <c r="G212" s="3" t="s">
         <v>75</v>
@@ -8935,10 +8908,10 @@
         <v>39</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J212" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K212" t="s">
         <v>63</v>
@@ -8946,7 +8919,7 @@
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B213" s="4">
         <v>3.7499999999999999E-2</v>
@@ -8955,13 +8928,13 @@
         <v>143</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E213" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F213" s="2" t="s">
-        <v>172</v>
+      <c r="F213" s="2">
+        <v>46106</v>
       </c>
       <c r="G213" s="3" t="s">
         <v>75</v>
@@ -8976,12 +8949,12 @@
         <v>62</v>
       </c>
       <c r="K213" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B214" s="4">
         <v>3.7499999999999999E-2</v>
@@ -8990,13 +8963,13 @@
         <v>143</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E214" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F214" s="2" t="s">
-        <v>172</v>
+      <c r="F214" s="2">
+        <v>46106</v>
       </c>
       <c r="G214" s="3" t="s">
         <v>75</v>
@@ -9005,10 +8978,10 @@
         <v>39</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J214" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K214" s="3" t="s">
         <v>42</v>
@@ -9016,13 +8989,13 @@
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B215" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>131</v>
@@ -9030,20 +9003,20 @@
       <c r="E215" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F215" s="2" t="s">
+      <c r="F215" s="2">
+        <v>46106</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="I215" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G215" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H215" s="3" t="s">
+      <c r="J215" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="I215" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J215" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="K215" s="3" t="s">
         <v>73</v>
@@ -9051,13 +9024,13 @@
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B216" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D216" s="3" t="s">
         <v>132</v>
@@ -9065,20 +9038,20 @@
       <c r="E216" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F216" s="2" t="s">
+      <c r="F216" s="2">
+        <v>46106</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I216" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="G216" s="3" t="s">
+      <c r="J216" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="H216" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I216" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="J216" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="K216" s="3" t="s">
         <v>73</v>
@@ -9086,13 +9059,13 @@
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B217" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D217" s="3" t="s">
         <v>131</v>
@@ -9100,17 +9073,17 @@
       <c r="E217" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F217" s="2" t="s">
-        <v>172</v>
+      <c r="F217" s="2">
+        <v>46106</v>
       </c>
       <c r="G217" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H217" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J217" s="3" t="s">
         <v>44</v>
@@ -9121,13 +9094,13 @@
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B218" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D218" s="3" t="s">
         <v>132</v>
@@ -9135,17 +9108,17 @@
       <c r="E218" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F218" s="2" t="s">
-        <v>172</v>
+      <c r="F218" s="2">
+        <v>46106</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H218" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J218" s="3" t="s">
         <v>44</v>
@@ -9156,13 +9129,13 @@
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B219" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D219" s="3" t="s">
         <v>131</v>
@@ -9170,17 +9143,17 @@
       <c r="E219" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F219" s="2" t="s">
-        <v>172</v>
+      <c r="F219" s="2">
+        <v>46106</v>
       </c>
       <c r="G219" s="3" t="s">
         <v>5</v>
       </c>
       <c r="H219" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J219" s="3" t="s">
         <v>6</v>
@@ -9191,13 +9164,13 @@
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B220" s="4">
         <v>3.125E-2</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D220" s="3" t="s">
         <v>132</v>
@@ -9205,17 +9178,17 @@
       <c r="E220" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F220" s="2" t="s">
-        <v>172</v>
+      <c r="F220" s="2">
+        <v>46106</v>
       </c>
       <c r="G220" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H220" s="3" t="s">
         <v>5</v>
       </c>
       <c r="I220" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J220" s="3" t="s">
         <v>6</v>
@@ -9226,7 +9199,7 @@
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B221" s="4">
         <v>6.5277777777777782E-2</v>
@@ -9235,13 +9208,13 @@
         <v>143</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E221" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F221" s="2" t="s">
-        <v>172</v>
+      <c r="F221" s="2">
+        <v>46106</v>
       </c>
       <c r="G221" s="3" t="s">
         <v>5</v>
@@ -9250,7 +9223,7 @@
         <v>75</v>
       </c>
       <c r="I221" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J221" s="3" t="s">
         <v>6</v>
@@ -9261,7 +9234,7 @@
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B222" s="4">
         <v>3.7499999999999999E-2</v>
@@ -9270,13 +9243,13 @@
         <v>143</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E222" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F222" s="2" t="s">
-        <v>172</v>
+      <c r="F222" s="2">
+        <v>46106</v>
       </c>
       <c r="G222" s="3" t="s">
         <v>75</v>
@@ -9285,7 +9258,7 @@
         <v>39</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J222" s="3" t="s">
         <v>6</v>
@@ -9296,7 +9269,7 @@
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B223" s="4">
         <v>6.5277777777777782E-2</v>
@@ -9305,13 +9278,13 @@
         <v>143</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E223" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F223" s="2" t="s">
-        <v>172</v>
+      <c r="F223" s="2">
+        <v>46106</v>
       </c>
       <c r="G223" s="3" t="s">
         <v>5</v>
@@ -9326,12 +9299,12 @@
         <v>62</v>
       </c>
       <c r="K223" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B224" s="4">
         <v>6.5277777777777782E-2</v>
@@ -9340,13 +9313,13 @@
         <v>143</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E224" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F224" s="2" t="s">
-        <v>172</v>
+      <c r="F224" s="2">
+        <v>46106</v>
       </c>
       <c r="G224" s="3" t="s">
         <v>5</v>
@@ -9355,10 +9328,10 @@
         <v>75</v>
       </c>
       <c r="I224" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J224" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K224" s="3" t="s">
         <v>42</v>
@@ -9366,7 +9339,7 @@
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B225" s="4">
         <v>6.5277777777777782E-2</v>
@@ -9375,13 +9348,13 @@
         <v>143</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E225" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F225" s="2" t="s">
-        <v>172</v>
+      <c r="F225" s="2">
+        <v>46106</v>
       </c>
       <c r="G225" s="3" t="s">
         <v>5</v>
@@ -9390,10 +9363,10 @@
         <v>75</v>
       </c>
       <c r="I225" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J225" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K225" s="3" t="s">
         <v>42</v>
@@ -9401,7 +9374,7 @@
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B226" s="4">
         <v>3.7499999999999999E-2</v>
@@ -9410,13 +9383,13 @@
         <v>143</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E226" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F226" s="2" t="s">
-        <v>172</v>
+      <c r="F226" s="2">
+        <v>46106</v>
       </c>
       <c r="G226" s="3" t="s">
         <v>75</v>
@@ -9425,10 +9398,10 @@
         <v>39</v>
       </c>
       <c r="I226" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J226" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K226" s="3" t="s">
         <v>42</v>
@@ -9436,7 +9409,7 @@
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B227" s="4">
         <v>6.5277777777777782E-2</v>
@@ -9445,13 +9418,13 @@
         <v>143</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E227" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F227" s="2" t="s">
-        <v>172</v>
+      <c r="F227" s="2">
+        <v>46106</v>
       </c>
       <c r="G227" s="3" t="s">
         <v>5</v>
@@ -9460,7 +9433,7 @@
         <v>75</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="J227" t="s">
         <v>62</v>
@@ -9471,34 +9444,34 @@
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B228" s="4">
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E228" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F228" s="2">
+        <v>46108</v>
       </c>
       <c r="G228" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J228" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K228" t="s">
         <v>63</v>
@@ -9506,34 +9479,34 @@
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B229" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E229" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F229" s="2">
+        <v>46108</v>
       </c>
       <c r="G229" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H229" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J229" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K229" t="s">
         <v>63</v>
@@ -9541,34 +9514,34 @@
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B230" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E230" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F230" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F230" s="2">
+        <v>46108</v>
       </c>
       <c r="G230" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="H230" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J230" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K230" t="s">
         <v>63</v>
@@ -9576,34 +9549,34 @@
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B231" s="4">
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E231" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F231" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F231" s="2">
+        <v>46108</v>
       </c>
       <c r="G231" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H231" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I231" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J231" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K231" t="s">
         <v>63</v>
@@ -9611,34 +9584,34 @@
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B232" s="4">
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E232" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F232" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F232" s="2">
+        <v>46108</v>
       </c>
       <c r="G232" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J232" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K232" s="3" t="s">
         <v>73</v>
@@ -9646,34 +9619,34 @@
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B233" s="4">
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E233" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F233" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F233" s="2">
+        <v>46108</v>
       </c>
       <c r="G233" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H233" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J233" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K233" s="3" t="s">
         <v>73</v>
@@ -9681,31 +9654,31 @@
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B234" s="4">
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E234" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F234" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F234" s="2">
+        <v>46108</v>
       </c>
       <c r="G234" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H234" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J234" s="3" t="s">
         <v>6</v>
@@ -9716,31 +9689,31 @@
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B235" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E235" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F235" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F235" s="2">
+        <v>46108</v>
       </c>
       <c r="G235" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H235" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J235" s="3" t="s">
         <v>6</v>
@@ -9751,31 +9724,31 @@
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A236" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B236" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E236" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F236" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F236" s="2">
+        <v>46108</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I236" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J236" s="3" t="s">
         <v>6</v>
@@ -9786,31 +9759,31 @@
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A237" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B237" s="4">
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E237" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F237" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F237" s="2">
+        <v>46108</v>
       </c>
       <c r="G237" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H237" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J237" s="3" t="s">
         <v>6</v>
@@ -9821,34 +9794,34 @@
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A238" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B238" s="4">
         <v>3.3333333333333333E-2</v>
       </c>
       <c r="C238" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E238" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F238" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F238" s="2">
+        <v>46108</v>
       </c>
       <c r="G238" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H238" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="I238" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J238" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K238" s="3" t="s">
         <v>42</v>
@@ -9856,34 +9829,34 @@
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A239" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B239" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C239" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E239" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F239" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F239" s="2">
+        <v>46108</v>
       </c>
       <c r="G239" s="3" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H239" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="I239" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J239" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K239" s="3" t="s">
         <v>42</v>
@@ -9891,34 +9864,34 @@
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A240" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B240" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="C240" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="E240" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F240" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F240" s="2">
+        <v>46108</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="I240" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J240" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K240" s="3" t="s">
         <v>42</v>
@@ -9926,34 +9899,34 @@
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A241" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="B241" s="4">
         <v>2.0833333333333332E-2</v>
       </c>
       <c r="C241" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="E241" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="F241" s="2" t="s">
-        <v>205</v>
+        <v>196</v>
+      </c>
+      <c r="F241" s="2">
+        <v>46108</v>
       </c>
       <c r="G241" s="3" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H241" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J241" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K241" s="3" t="s">
         <v>42</v>
@@ -9961,7 +9934,7 @@
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A242" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B242" s="4">
         <v>2.361111111111111E-2</v>
@@ -9970,25 +9943,25 @@
         <v>143</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E242" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F242" s="2" t="s">
-        <v>190</v>
+      <c r="F242" s="2">
+        <v>46109</v>
       </c>
       <c r="G242" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I242" s="3" t="s">
         <v>11</v>
       </c>
       <c r="J242" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="K242" t="s">
         <v>67</v>
@@ -9996,7 +9969,7 @@
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A243" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B243" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10005,16 +9978,16 @@
         <v>143</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E243" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F243" s="2" t="s">
-        <v>190</v>
+      <c r="F243" s="2">
+        <v>46109</v>
       </c>
       <c r="G243" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H243" s="3" t="s">
         <v>39</v>
@@ -10023,7 +9996,7 @@
         <v>11</v>
       </c>
       <c r="J243" s="3" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="K243" t="s">
         <v>67</v>
@@ -10031,7 +10004,7 @@
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A244" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B244" s="4">
         <v>2.361111111111111E-2</v>
@@ -10040,25 +10013,25 @@
         <v>143</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E244" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F244" s="2" t="s">
-        <v>190</v>
+      <c r="F244" s="2">
+        <v>46109</v>
       </c>
       <c r="G244" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H244" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J244" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K244" t="s">
         <v>63</v>
@@ -10066,7 +10039,7 @@
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A245" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B245" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10075,25 +10048,25 @@
         <v>143</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E245" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F245" s="2" t="s">
-        <v>190</v>
+      <c r="F245" s="2">
+        <v>46109</v>
       </c>
       <c r="G245" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H245" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I245" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J245" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K245" t="s">
         <v>63</v>
@@ -10101,7 +10074,7 @@
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A246" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B246" s="4">
         <v>2.361111111111111E-2</v>
@@ -10110,22 +10083,22 @@
         <v>143</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E246" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F246" s="2" t="s">
-        <v>190</v>
+      <c r="F246" s="2">
+        <v>46109</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H246" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I246" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J246" s="3" t="s">
         <v>6</v>
@@ -10136,7 +10109,7 @@
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A247" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B247" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10145,22 +10118,22 @@
         <v>143</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E247" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F247" s="2" t="s">
-        <v>190</v>
+      <c r="F247" s="2">
+        <v>46109</v>
       </c>
       <c r="G247" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H247" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I247" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J247" s="3" t="s">
         <v>6</v>
@@ -10171,7 +10144,7 @@
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A248" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B248" s="4">
         <v>2.361111111111111E-2</v>
@@ -10180,25 +10153,25 @@
         <v>143</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E248" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F248" s="2" t="s">
-        <v>190</v>
+      <c r="F248" s="2">
+        <v>46109</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H248" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I248" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J248" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K248" s="3" t="s">
         <v>73</v>
@@ -10206,7 +10179,7 @@
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A249" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B249" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10215,25 +10188,25 @@
         <v>143</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E249" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F249" s="2" t="s">
-        <v>190</v>
+      <c r="F249" s="2">
+        <v>46109</v>
       </c>
       <c r="G249" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H249" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J249" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K249" s="3" t="s">
         <v>73</v>
@@ -10241,7 +10214,7 @@
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A250" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B250" s="4">
         <v>2.361111111111111E-2</v>
@@ -10250,25 +10223,25 @@
         <v>143</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E250" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F250" s="2" t="s">
-        <v>190</v>
+      <c r="F250" s="2">
+        <v>46109</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H250" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I250" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J250" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K250" s="3" t="s">
         <v>73</v>
@@ -10276,7 +10249,7 @@
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A251" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B251" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10285,25 +10258,25 @@
         <v>143</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E251" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F251" s="2" t="s">
-        <v>190</v>
+      <c r="F251" s="2">
+        <v>46109</v>
       </c>
       <c r="G251" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H251" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I251" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J251" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K251" s="3" t="s">
         <v>73</v>
@@ -10311,7 +10284,7 @@
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A252" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B252" s="4">
         <v>2.361111111111111E-2</v>
@@ -10320,25 +10293,25 @@
         <v>143</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E252" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F252" s="2" t="s">
-        <v>190</v>
+      <c r="F252" s="2">
+        <v>46109</v>
       </c>
       <c r="G252" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H252" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I252" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J252" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K252" s="3" t="s">
         <v>42</v>
@@ -10346,7 +10319,7 @@
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A253" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B253" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10355,25 +10328,25 @@
         <v>143</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E253" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F253" s="2" t="s">
-        <v>190</v>
+      <c r="F253" s="2">
+        <v>46109</v>
       </c>
       <c r="G253" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H253" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I253" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J253" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K253" s="3" t="s">
         <v>42</v>
@@ -10381,7 +10354,7 @@
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A254" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B254" s="4">
         <v>2.361111111111111E-2</v>
@@ -10390,25 +10363,25 @@
         <v>143</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E254" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F254" s="2" t="s">
-        <v>190</v>
+      <c r="F254" s="2">
+        <v>46109</v>
       </c>
       <c r="G254" s="3" t="s">
         <v>39</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="I254" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J254" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K254" s="3" t="s">
         <v>42</v>
@@ -10416,7 +10389,7 @@
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A255" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B255" s="4">
         <v>2.2222222222222223E-2</v>
@@ -10425,25 +10398,25 @@
         <v>143</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="E255" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F255" s="2" t="s">
-        <v>190</v>
+      <c r="F255" s="2">
+        <v>46109</v>
       </c>
       <c r="G255" s="3" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H255" s="3" t="s">
         <v>39</v>
       </c>
       <c r="I255" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J255" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K255" s="3" t="s">
         <v>42</v>
@@ -10451,7 +10424,7 @@
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A256" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B256" s="4">
         <v>5.8333333333333334E-2</v>
@@ -10460,13 +10433,13 @@
         <v>143</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E256" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F256" s="2" t="s">
-        <v>196</v>
+      <c r="F256" s="2">
+        <v>46110</v>
       </c>
       <c r="G256" s="3" t="s">
         <v>39</v>
@@ -10475,7 +10448,7 @@
         <v>96</v>
       </c>
       <c r="I256" s="3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="J256" s="3" t="s">
         <v>90</v>
@@ -10486,7 +10459,7 @@
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A257" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B257" s="4">
         <v>5.8333333333333334E-2</v>
@@ -10495,13 +10468,13 @@
         <v>143</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E257" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F257" s="2" t="s">
-        <v>196</v>
+      <c r="F257" s="2">
+        <v>46110</v>
       </c>
       <c r="G257" s="3" t="s">
         <v>39</v>
@@ -10510,7 +10483,7 @@
         <v>96</v>
       </c>
       <c r="I257" s="3" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="J257" s="3" t="s">
         <v>130</v>
@@ -10521,7 +10494,7 @@
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A258" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B258" s="4">
         <v>5.8333333333333334E-2</v>
@@ -10530,13 +10503,13 @@
         <v>143</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E258" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F258" s="2" t="s">
-        <v>196</v>
+      <c r="F258" s="2">
+        <v>46110</v>
       </c>
       <c r="G258" s="3" t="s">
         <v>39</v>
@@ -10545,10 +10518,10 @@
         <v>96</v>
       </c>
       <c r="I258" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J258" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K258" t="s">
         <v>63</v>
@@ -10556,7 +10529,7 @@
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A259" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B259" s="4">
         <v>5.8333333333333334E-2</v>
@@ -10565,13 +10538,13 @@
         <v>143</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E259" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F259" s="2" t="s">
-        <v>196</v>
+      <c r="F259" s="2">
+        <v>46110</v>
       </c>
       <c r="G259" s="3" t="s">
         <v>39</v>
@@ -10580,7 +10553,7 @@
         <v>96</v>
       </c>
       <c r="I259" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J259" s="3" t="s">
         <v>6</v>
@@ -10591,7 +10564,7 @@
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A260" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B260" s="4">
         <v>5.8333333333333334E-2</v>
@@ -10600,13 +10573,13 @@
         <v>143</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E260" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F260" s="2" t="s">
-        <v>196</v>
+      <c r="F260" s="2">
+        <v>46110</v>
       </c>
       <c r="G260" s="3" t="s">
         <v>39</v>
@@ -10615,10 +10588,10 @@
         <v>96</v>
       </c>
       <c r="I260" s="3" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J260" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K260" s="3" t="s">
         <v>73</v>
@@ -10626,7 +10599,7 @@
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A261" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B261" s="4">
         <v>5.8333333333333334E-2</v>
@@ -10635,13 +10608,13 @@
         <v>143</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="E261" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F261" s="2" t="s">
-        <v>196</v>
+      <c r="F261" s="2">
+        <v>46110</v>
       </c>
       <c r="G261" s="3" t="s">
         <v>39</v>
@@ -10650,10 +10623,10 @@
         <v>96</v>
       </c>
       <c r="I261" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J261" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K261" s="3" t="s">
         <v>73</v>
@@ -10661,7 +10634,7 @@
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A262" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B262" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10670,13 +10643,13 @@
         <v>143</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E262" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F262" s="2" t="s">
-        <v>200</v>
+      <c r="F262" s="2">
+        <v>46112</v>
       </c>
       <c r="G262" s="3" t="s">
         <v>5</v>
@@ -10685,10 +10658,10 @@
         <v>133</v>
       </c>
       <c r="I262" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="J262" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K262" t="s">
         <v>63</v>
@@ -10696,7 +10669,7 @@
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A263" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B263" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10705,13 +10678,13 @@
         <v>143</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E263" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F263" s="2" t="s">
-        <v>200</v>
+      <c r="F263" s="2">
+        <v>46112</v>
       </c>
       <c r="G263" s="3" t="s">
         <v>5</v>
@@ -10731,7 +10704,7 @@
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A264" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B264" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10740,13 +10713,13 @@
         <v>143</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E264" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F264" s="2" t="s">
-        <v>200</v>
+      <c r="F264" s="2">
+        <v>46112</v>
       </c>
       <c r="G264" s="3" t="s">
         <v>96</v>
@@ -10755,10 +10728,10 @@
         <v>5</v>
       </c>
       <c r="I264" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="J264" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K264" t="s">
         <v>63</v>
@@ -10766,7 +10739,7 @@
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A265" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B265" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10775,13 +10748,13 @@
         <v>143</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E265" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F265" s="2" t="s">
-        <v>200</v>
+      <c r="F265" s="2">
+        <v>46112</v>
       </c>
       <c r="G265" s="3" t="s">
         <v>96</v>
@@ -10790,18 +10763,18 @@
         <v>5</v>
       </c>
       <c r="I265" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="J265" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K265" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A266" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B266" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10810,13 +10783,13 @@
         <v>143</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E266" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F266" s="2" t="s">
-        <v>200</v>
+      <c r="F266" s="2">
+        <v>46112</v>
       </c>
       <c r="G266" s="3" t="s">
         <v>5</v>
@@ -10825,10 +10798,10 @@
         <v>133</v>
       </c>
       <c r="I266" s="3" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="J266" s="3" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="K266" t="s">
         <v>45</v>
@@ -10836,7 +10809,7 @@
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A267" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B267" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10845,13 +10818,13 @@
         <v>143</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E267" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F267" s="2" t="s">
-        <v>200</v>
+      <c r="F267" s="2">
+        <v>46112</v>
       </c>
       <c r="G267" s="3" t="s">
         <v>5</v>
@@ -10860,10 +10833,10 @@
         <v>133</v>
       </c>
       <c r="I267" s="3" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="J267" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K267" s="3" t="s">
         <v>73</v>
@@ -10871,7 +10844,7 @@
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A268" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B268" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10880,13 +10853,13 @@
         <v>143</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E268" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F268" s="2" t="s">
-        <v>200</v>
+      <c r="F268" s="2">
+        <v>46112</v>
       </c>
       <c r="G268" s="3" t="s">
         <v>96</v>
@@ -10895,7 +10868,7 @@
         <v>5</v>
       </c>
       <c r="I268" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J268" s="3" t="s">
         <v>6</v>
@@ -10906,7 +10879,7 @@
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A269" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B269" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10915,13 +10888,13 @@
         <v>143</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E269" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F269" s="2" t="s">
-        <v>200</v>
+      <c r="F269" s="2">
+        <v>46112</v>
       </c>
       <c r="G269" s="3" t="s">
         <v>5</v>
@@ -10930,7 +10903,7 @@
         <v>133</v>
       </c>
       <c r="I269" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="J269" s="3" t="s">
         <v>6</v>
@@ -10941,7 +10914,7 @@
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A270" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B270" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10950,13 +10923,13 @@
         <v>143</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E270" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F270" s="2" t="s">
-        <v>200</v>
+      <c r="F270" s="2">
+        <v>46112</v>
       </c>
       <c r="G270" s="3" t="s">
         <v>96</v>
@@ -10965,10 +10938,10 @@
         <v>5</v>
       </c>
       <c r="I270" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="J270" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="K270" s="3" t="s">
         <v>42</v>
@@ -10976,7 +10949,7 @@
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A271" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B271" s="4">
         <v>2.8472222222222222E-2</v>
@@ -10985,13 +10958,13 @@
         <v>143</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E271" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F271" s="2" t="s">
-        <v>200</v>
+      <c r="F271" s="2">
+        <v>46112</v>
       </c>
       <c r="G271" s="3" t="s">
         <v>96</v>
@@ -11000,10 +10973,10 @@
         <v>5</v>
       </c>
       <c r="I271" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J271" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K271" s="3" t="s">
         <v>42</v>
@@ -11011,7 +10984,7 @@
     </row>
     <row r="272" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A272" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B272" s="4">
         <v>2.8472222222222222E-2</v>
@@ -11020,13 +10993,13 @@
         <v>143</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="E272" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F272" s="2" t="s">
-        <v>200</v>
+      <c r="F272" s="2">
+        <v>46112</v>
       </c>
       <c r="G272" s="3" t="s">
         <v>5</v>
@@ -11035,10 +11008,10 @@
         <v>133</v>
       </c>
       <c r="I272" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="J272" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K272" s="3" t="s">
         <v>42</v>
